--- a/project/graphic_designing/encoded_letters.xlsx
+++ b/project/graphic_designing/encoded_letters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joelk\Documents\ee_files\EE2026\project\graphic_designing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1392200-F42B-465C-BEB9-A0A0A4C09B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A50F4E-A826-4F66-A277-96125A9AC39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{3F09DA75-48F6-4CED-A1E4-6F4F2B560964}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F09DA75-48F6-4CED-A1E4-6F4F2B560964}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Encoding" sheetId="1" r:id="rId1"/>
@@ -7408,5 +7408,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/project/graphic_designing/encoded_letters.xlsx
+++ b/project/graphic_designing/encoded_letters.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joelk\Documents\ee_files\EE2026\project\graphic_designing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A50F4E-A826-4F66-A277-96125A9AC39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CABE00-EE5E-4778-869C-A018DF7F86BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F09DA75-48F6-4CED-A1E4-6F4F2B560964}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3F09DA75-48F6-4CED-A1E4-6F4F2B560964}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Encoding" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -62,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="66">
   <si>
     <t>Char</t>
   </si>
@@ -312,529 +309,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="menu mockup"/>
-      <sheetName val="modify this"/>
-      <sheetName val="only read from this"/>
-      <sheetName val="Letter Encodings"/>
-      <sheetName val="Sheet2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Char</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Hex</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>A</v>
-          </cell>
-          <cell r="C2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>B</v>
-          </cell>
-          <cell r="C3">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>C</v>
-          </cell>
-          <cell r="C4">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>D</v>
-          </cell>
-          <cell r="C5">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>E</v>
-          </cell>
-          <cell r="C6">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>F</v>
-          </cell>
-          <cell r="C7">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>G</v>
-          </cell>
-          <cell r="C8">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>H</v>
-          </cell>
-          <cell r="C9">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>I</v>
-          </cell>
-          <cell r="C10">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>J</v>
-          </cell>
-          <cell r="C11">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>K</v>
-          </cell>
-          <cell r="C12">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>L</v>
-          </cell>
-          <cell r="C13">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>M</v>
-          </cell>
-          <cell r="C14">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="C15">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>O</v>
-          </cell>
-          <cell r="C16">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="C17">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>Q</v>
-          </cell>
-          <cell r="C18">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>R</v>
-          </cell>
-          <cell r="C19">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>S</v>
-          </cell>
-          <cell r="C20">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>T</v>
-          </cell>
-          <cell r="C21">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>U</v>
-          </cell>
-          <cell r="C22">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>V</v>
-          </cell>
-          <cell r="C23">
-            <v>21</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>W</v>
-          </cell>
-          <cell r="C24">
-            <v>22</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>X</v>
-          </cell>
-          <cell r="C25">
-            <v>23</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>Y</v>
-          </cell>
-          <cell r="C26">
-            <v>24</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>Z</v>
-          </cell>
-          <cell r="C27">
-            <v>25</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>a</v>
-          </cell>
-          <cell r="C28">
-            <v>26</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>b</v>
-          </cell>
-          <cell r="C29">
-            <v>27</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>c</v>
-          </cell>
-          <cell r="C30">
-            <v>28</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>d</v>
-          </cell>
-          <cell r="C31">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>e</v>
-          </cell>
-          <cell r="C32">
-            <v>30</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="C33">
-            <v>31</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>g</v>
-          </cell>
-          <cell r="C34">
-            <v>32</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>h</v>
-          </cell>
-          <cell r="C35">
-            <v>33</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>i</v>
-          </cell>
-          <cell r="C36">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>j</v>
-          </cell>
-          <cell r="C37">
-            <v>35</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>k</v>
-          </cell>
-          <cell r="C38">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>l</v>
-          </cell>
-          <cell r="C39">
-            <v>37</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="C40">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>n</v>
-          </cell>
-          <cell r="C41">
-            <v>39</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>o</v>
-          </cell>
-          <cell r="C42">
-            <v>40</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="C43">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44" t="str">
-            <v>q</v>
-          </cell>
-          <cell r="C44">
-            <v>42</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="C45">
-            <v>43</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46" t="str">
-            <v>s</v>
-          </cell>
-          <cell r="C46">
-            <v>44</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47" t="str">
-            <v>t</v>
-          </cell>
-          <cell r="C47">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>u</v>
-          </cell>
-          <cell r="C48">
-            <v>46</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49" t="str">
-            <v>v</v>
-          </cell>
-          <cell r="C49">
-            <v>47</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50" t="str">
-            <v>w</v>
-          </cell>
-          <cell r="C50">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51" t="str">
-            <v>x</v>
-          </cell>
-          <cell r="C51">
-            <v>49</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52" t="str">
-            <v>y</v>
-          </cell>
-          <cell r="C52">
-            <v>50</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53" t="str">
-            <v>z</v>
-          </cell>
-          <cell r="C53">
-            <v>51</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54" t="str">
-            <v>(space)</v>
-          </cell>
-          <cell r="C54">
-            <v>52</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55" t="str">
-            <v>,</v>
-          </cell>
-          <cell r="C55">
-            <v>53</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56" t="str">
-            <v>.</v>
-          </cell>
-          <cell r="C56">
-            <v>54</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57" t="str">
-            <v>(</v>
-          </cell>
-          <cell r="C57">
-            <v>57</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>)</v>
-          </cell>
-          <cell r="C58">
-            <v>58</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>1</v>
-          </cell>
-          <cell r="C59">
-            <v>53</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>2</v>
-          </cell>
-          <cell r="C60">
-            <v>53</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>3</v>
-          </cell>
-          <cell r="C61">
-            <v>53</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>4</v>
-          </cell>
-          <cell r="C62">
-            <v>53</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2153,10 +1627,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57AE1B8-8CB2-44DB-A4DF-67661E1D3283}">
-  <dimension ref="A1:BS34"/>
+  <dimension ref="A1:BT34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2244,145 +1718,145 @@
       <c r="AC1" t="s">
         <v>34</v>
       </c>
-      <c r="AG1">
-        <f>COUNTA(A1:AF1)</f>
+      <c r="AH1">
+        <f>COUNTA(A1:AG1)</f>
         <v>29</v>
       </c>
-      <c r="AH1" cm="1">
-        <f t="array" ref="AH1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI1" cm="1">
+        <f t="array" ref="AI1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="AI1" cm="1">
-        <f t="array" ref="AI1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ1" cm="1">
+        <f t="array" ref="AJ1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AJ1" cm="1">
-        <f t="array" ref="AJ1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK1" cm="1">
+        <f t="array" ref="AK1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AK1" cm="1">
-        <f t="array" ref="AK1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL1" cm="1">
+        <f t="array" ref="AL1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AL1" cm="1">
-        <f t="array" ref="AL1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AM1" cm="1">
-        <f t="array" ref="AM1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AN1" cm="1">
+        <f t="array" ref="AN1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>48</v>
       </c>
-      <c r="AN1" cm="1">
-        <f t="array" ref="AN1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO1" cm="1">
+        <f t="array" ref="AO1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AO1" cm="1">
-        <f t="array" ref="AO1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AP1" cm="1">
-        <f t="array" ref="AP1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AP1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AQ1" cm="1">
+        <f t="array" ref="AQ1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AQ1" cm="1">
-        <f t="array" ref="AQ1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AR1" cm="1">
-        <f t="array" ref="AR1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AR1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AS1" cm="1">
-        <f t="array" ref="AS1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AT1" cm="1">
+        <f t="array" ref="AT1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AT1" cm="1">
-        <f t="array" ref="AT1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AU1" cm="1">
-        <f t="array" ref="AU1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AU1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AV1" cm="1">
+        <f t="array" ref="AV1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="AV1" cm="1">
-        <f t="array" ref="AV1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AW1" cm="1">
-        <f t="array" ref="AW1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AW1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AX1" cm="1">
+        <f t="array" ref="AX1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AX1" cm="1">
-        <f t="array" ref="AX1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AY1" cm="1">
+        <f t="array" ref="AY1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>55</v>
       </c>
-      <c r="AY1" cm="1">
-        <f t="array" ref="AY1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AZ1" cm="1">
+        <f t="array" ref="AZ1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>57</v>
       </c>
-      <c r="AZ1" cm="1">
-        <f t="array" ref="AZ1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>56</v>
-      </c>
       <c r="BA1" cm="1">
-        <f t="array" ref="BA1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="BA1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>56</v>
       </c>
       <c r="BB1" cm="1">
-        <f t="array" ref="BB1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="BB1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
       </c>
       <c r="BC1" cm="1">
-        <f t="array" ref="BC1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="BC1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
       </c>
       <c r="BD1" cm="1">
-        <f t="array" ref="BD1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="BD1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="BE1" cm="1">
-        <f t="array" ref="BE1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BE1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BF1" cm="1">
+        <f t="array" ref="BF1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BF1" cm="1">
-        <f t="array" ref="BF1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BG1" cm="1">
-        <f t="array" ref="BG1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BG1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BH1" cm="1">
+        <f t="array" ref="BH1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BH1" cm="1">
-        <f t="array" ref="BH1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BI1" cm="1">
+        <f t="array" ref="BI1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BI1" cm="1">
-        <f t="array" ref="BI1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BJ1" cm="1">
+        <f t="array" ref="BJ1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="BJ1" cm="1">
-        <f t="array" ref="BJ1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="BO1">
-        <f>COUNTA(AH1:BM1)</f>
+      <c r="BK1" cm="1">
+        <f t="array" ref="BK1">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC1, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BP1">
+        <f>COUNTA(AI1:BN1)</f>
         <v>29</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>61</v>
-      </c>
-      <c r="BQ1">
-        <v>1</v>
       </c>
       <c r="BR1">
         <v>1</v>
       </c>
-      <c r="BS1" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH1:BN1)</f>
+      <c r="BS1">
+        <v>1</v>
+      </c>
+      <c r="BT1" t="str">
+        <f t="shared" ref="BT1:BT34" si="0">_xlfn.TEXTJOIN(", ",TRUE,AI1:BO1)</f>
         <v>4, 26, 28, 33, 52, 48, 33, 34, 45, 30, 52, 41, 34, 49, 30, 37, 55, 57, 56, 52, 34, 44, 52, 26, 52, 39, 40, 29, 30</v>
       </c>
     </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -2461,127 +1935,127 @@
       <c r="Z2" t="s">
         <v>42</v>
       </c>
-      <c r="AG2">
-        <f t="shared" ref="AG2:AG34" si="0">COUNTA(A2:AF2)</f>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AH34" si="1">COUNTA(A2:AG2)</f>
         <v>26</v>
       </c>
-      <c r="AH2" cm="1">
-        <f t="array" ref="AH2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AI2" cm="1">
-        <f t="array" ref="AI2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AI2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AJ2" cm="1">
+        <f t="array" ref="AJ2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AJ2" cm="1">
-        <f t="array" ref="AJ2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AK2" cm="1">
-        <f t="array" ref="AK2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AK2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AL2" cm="1">
+        <f t="array" ref="AL2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AL2" cm="1">
-        <f t="array" ref="AL2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AM2" cm="1">
-        <f t="array" ref="AM2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AN2" cm="1">
+        <f t="array" ref="AN2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AN2" cm="1">
-        <f t="array" ref="AN2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AO2" cm="1">
-        <f t="array" ref="AO2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="AO2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AP2" cm="1">
-        <f t="array" ref="AP2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AP2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AQ2" cm="1">
+        <f t="array" ref="AQ2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AQ2" cm="1">
-        <f t="array" ref="AQ2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR2" cm="1">
+        <f t="array" ref="AR2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AR2" cm="1">
-        <f t="array" ref="AR2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AS2" cm="1">
-        <f t="array" ref="AS2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AT2" cm="1">
+        <f t="array" ref="AT2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AT2" cm="1">
-        <f t="array" ref="AT2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AU2" cm="1">
-        <f t="array" ref="AU2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="AU2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AV2" cm="1">
-        <f t="array" ref="AV2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AV2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AW2" cm="1">
+        <f t="array" ref="AW2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AW2" cm="1">
-        <f t="array" ref="AW2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AX2" cm="1">
+        <f t="array" ref="AX2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AX2" cm="1">
-        <f t="array" ref="AX2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AY2" cm="1">
+        <f t="array" ref="AY2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AY2" cm="1">
-        <f t="array" ref="AY2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AZ2" cm="1">
+        <f t="array" ref="AZ2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AZ2" cm="1">
-        <f t="array" ref="AZ2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BA2" cm="1">
+        <f t="array" ref="BA2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="BA2" cm="1">
-        <f t="array" ref="BA2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="BB2" cm="1">
-        <f t="array" ref="BB2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="BB2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="BC2" cm="1">
-        <f t="array" ref="BC2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="BC2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="BD2" cm="1">
-        <f t="array" ref="BD2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BD2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BE2" cm="1">
+        <f t="array" ref="BE2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>31</v>
       </c>
-      <c r="BE2" cm="1">
-        <f t="array" ref="BE2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BF2" cm="1">
+        <f t="array" ref="BF2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BF2" cm="1">
-        <f t="array" ref="BF2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="BG2" cm="1">
-        <f t="array" ref="BG2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BG2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="BH2" cm="1">
+        <f t="array" ref="BH2">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z2, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="BO2">
-        <f t="shared" ref="BO2:BO34" si="1">COUNTA(AH2:BM2)</f>
+      <c r="BP2">
+        <f t="shared" ref="BP2:BP34" si="2">COUNTA(AI2:BN2)</f>
         <v>26</v>
       </c>
-      <c r="BR2">
+      <c r="BS2">
         <v>2</v>
       </c>
-      <c r="BS2" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH2:BN2)</f>
+      <c r="BT2" t="str">
+        <f t="shared" si="0"/>
         <v>34, 39, 52, 26, 52, 32, 43, 34, 29, 53, 52, 39, 30, 34, 32, 33, 27, 40, 46, 43, 44, 52, 31, 40, 43, 38</v>
       </c>
     </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -2600,47 +2074,47 @@
       <c r="F3" t="s">
         <v>58</v>
       </c>
-      <c r="AG3">
-        <f t="shared" si="0"/>
+      <c r="AH3">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="AH3" cm="1">
-        <f t="array" ref="AH3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AI3" cm="1">
-        <f t="array" ref="AI3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AI3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AJ3" cm="1">
+        <f t="array" ref="AJ3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AJ3" cm="1">
-        <f t="array" ref="AJ3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK3" cm="1">
+        <f t="array" ref="AK3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AK3" cm="1">
-        <f t="array" ref="AK3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AL3" cm="1">
-        <f t="array" ref="AL3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="AL3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AM3" cm="1">
-        <f t="array" ref="AM3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="AN3" cm="1">
+        <f t="array" ref="AN3">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F3, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="BO3">
-        <f t="shared" si="1"/>
+      <c r="BP3">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="BR3">
+      <c r="BS3">
         <v>3</v>
       </c>
-      <c r="BS3" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH3:BN3)</f>
+      <c r="BT3" t="str">
+        <f t="shared" si="0"/>
         <v>30, 29, 32, 30, 44, 54</v>
       </c>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2734,150 +2208,150 @@
       <c r="AE4" t="s">
         <v>33</v>
       </c>
-      <c r="AG4">
-        <f t="shared" si="0"/>
+      <c r="AH4">
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="AH4" cm="1">
-        <f t="array" ref="AH4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI4" cm="1">
+        <f t="array" ref="AI4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="AI4" cm="1">
-        <f t="array" ref="AI4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ4" cm="1">
+        <f t="array" ref="AJ4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AJ4" cm="1">
-        <f t="array" ref="AJ4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AK4" cm="1">
-        <f t="array" ref="AK4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AK4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AL4" cm="1">
-        <f t="array" ref="AL4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AL4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AM4" cm="1">
+        <f t="array" ref="AM4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>11</v>
       </c>
-      <c r="AM4" cm="1">
-        <f t="array" ref="AM4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AN4" cm="1">
-        <f t="array" ref="AN4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AN4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AO4" cm="1">
+        <f t="array" ref="AO4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>31</v>
       </c>
-      <c r="AO4" cm="1">
-        <f t="array" ref="AO4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP4" cm="1">
+        <f t="array" ref="AP4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AP4" cm="1">
-        <f t="array" ref="AP4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ4" cm="1">
+        <f t="array" ref="AQ4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AQ4" cm="1">
-        <f t="array" ref="AQ4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AR4" cm="1">
-        <f t="array" ref="AR4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AR4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AS4" cm="1">
+        <f t="array" ref="AS4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="AS4" cm="1">
-        <f t="array" ref="AS4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AT4" cm="1">
+        <f t="array" ref="AT4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AT4" cm="1">
-        <f t="array" ref="AT4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AU4" cm="1">
+        <f t="array" ref="AU4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AU4" cm="1">
-        <f t="array" ref="AU4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AV4" cm="1">
-        <f t="array" ref="AV4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
+        <f t="array" ref="AV4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AW4" cm="1">
-        <f t="array" ref="AW4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AW4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AX4" cm="1">
-        <f t="array" ref="AX4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AY4" cm="1">
+        <f t="array" ref="AY4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>11</v>
       </c>
-      <c r="AY4" cm="1">
-        <f t="array" ref="AY4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AZ4" cm="1">
-        <f t="array" ref="AZ4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AZ4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BA4" cm="1">
+        <f t="array" ref="BA4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>31</v>
       </c>
-      <c r="BA4" cm="1">
-        <f t="array" ref="BA4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BB4" cm="1">
+        <f t="array" ref="BB4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BB4" cm="1">
-        <f t="array" ref="BB4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BC4" cm="1">
+        <f t="array" ref="BC4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="BC4" cm="1">
-        <f t="array" ref="BC4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BD4" cm="1">
-        <f t="array" ref="BD4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BD4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BE4" cm="1">
+        <f t="array" ref="BE4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="BE4" cm="1">
-        <f t="array" ref="BE4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BF4" cm="1">
+        <f t="array" ref="BF4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="BF4" cm="1">
-        <f t="array" ref="BF4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BG4" cm="1">
+        <f t="array" ref="BG4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="BG4" cm="1">
-        <f t="array" ref="BG4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="BH4" cm="1">
-        <f t="array" ref="BH4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
+        <f t="array" ref="BH4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="BI4" cm="1">
-        <f t="array" ref="BI4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="BI4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="BJ4" cm="1">
-        <f t="array" ref="BJ4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BJ4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BK4" cm="1">
+        <f t="array" ref="BK4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BK4" cm="1">
-        <f t="array" ref="BK4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BL4" cm="1">
+        <f t="array" ref="BL4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BL4" cm="1">
-        <f t="array" ref="BL4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AE4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BM4" cm="1">
+        <f t="array" ref="BM4">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AE4, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="BO4">
-        <f t="shared" si="1"/>
+      <c r="BP4">
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BQ4">
+      <c r="BR4">
         <v>2</v>
       </c>
-      <c r="BR4">
+      <c r="BS4">
         <v>4</v>
       </c>
-      <c r="BS4" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH4:BN4)</f>
+      <c r="BT4" t="str">
+        <f t="shared" si="0"/>
         <v>5, 40, 43, 52, 11, 30, 31, 45, 53, 52, 20, 41, 41, 30, 43, 52, 11, 30, 31, 45, 53, 52, 20, 41, 41, 30, 43, 52, 26, 39, 29</v>
       </c>
     </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -2965,139 +2439,139 @@
       <c r="AC5" t="s">
         <v>47</v>
       </c>
-      <c r="AG5">
-        <f t="shared" si="0"/>
+      <c r="AH5">
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="AH5" cm="1">
-        <f t="array" ref="AH5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI5" cm="1">
+        <f t="array" ref="AI5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="AI5" cm="1">
-        <f t="array" ref="AI5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ5" cm="1">
+        <f t="array" ref="AJ5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AJ5" cm="1">
-        <f t="array" ref="AJ5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK5" cm="1">
+        <f t="array" ref="AK5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AK5" cm="1">
-        <f t="array" ref="AK5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AL5" cm="1">
-        <f t="array" ref="AL5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
+        <f t="array" ref="AL5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AM5" cm="1">
-        <f t="array" ref="AM5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AM5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AN5" cm="1">
-        <f t="array" ref="AN5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AN5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AO5" cm="1">
+        <f t="array" ref="AO5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>17</v>
       </c>
-      <c r="AO5" cm="1">
-        <f t="array" ref="AO5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AP5" cm="1">
-        <f t="array" ref="AP5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AP5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AQ5" cm="1">
+        <f t="array" ref="AQ5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AQ5" cm="1">
-        <f t="array" ref="AQ5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR5" cm="1">
+        <f t="array" ref="AR5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AR5" cm="1">
-        <f t="array" ref="AR5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AS5" cm="1">
+        <f t="array" ref="AS5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AS5" cm="1">
-        <f t="array" ref="AS5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AT5" cm="1">
-        <f t="array" ref="AT5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AT5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AU5" cm="1">
+        <f t="array" ref="AU5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AU5" cm="1">
-        <f t="array" ref="AU5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AV5" cm="1">
-        <f t="array" ref="AV5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AV5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AW5" cm="1">
+        <f t="array" ref="AW5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="AW5" cm="1">
-        <f t="array" ref="AW5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AX5" cm="1">
-        <f t="array" ref="AX5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AY5" cm="1">
+        <f t="array" ref="AY5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AY5" cm="1">
-        <f t="array" ref="AY5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AZ5" cm="1">
+        <f t="array" ref="AZ5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AZ5" cm="1">
-        <f t="array" ref="AZ5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BA5" cm="1">
-        <f t="array" ref="BA5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BA5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BB5" cm="1">
+        <f t="array" ref="BB5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>31</v>
       </c>
-      <c r="BB5" cm="1">
-        <f t="array" ref="BB5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="BC5" cm="1">
-        <f t="array" ref="BC5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BC5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BD5" cm="1">
+        <f t="array" ref="BD5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BD5" cm="1">
-        <f t="array" ref="BD5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BE5" cm="1">
+        <f t="array" ref="BE5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="BE5" cm="1">
-        <f t="array" ref="BE5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BF5" cm="1">
-        <f t="array" ref="BF5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BF5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BG5" cm="1">
+        <f t="array" ref="BG5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BG5" cm="1">
-        <f t="array" ref="BG5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BH5" cm="1">
+        <f t="array" ref="BH5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="BH5" cm="1">
-        <f t="array" ref="BH5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="BI5" cm="1">
-        <f t="array" ref="BI5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="BI5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="BJ5" cm="1">
-        <f t="array" ref="BJ5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
-      <c r="BO5">
-        <f t="shared" si="1"/>
+        <f t="array" ref="BJ5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BK5" cm="1">
+        <f t="array" ref="BK5">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC5, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="BP5">
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="BR5">
+      <c r="BS5">
         <v>5</v>
       </c>
-      <c r="BS5" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH5:BN5)</f>
+      <c r="BT5" t="str">
+        <f t="shared" si="0"/>
         <v>20, 41, 41, 30, 43, 52, 17, 34, 32, 33, 45, 52, 41, 34, 49, 30, 37, 53, 52, 31, 34, 39, 29, 52, 45, 33, 30, 34, 43</v>
       </c>
     </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -3194,161 +2668,168 @@
       <c r="AF6" t="s">
         <v>48</v>
       </c>
-      <c r="AG6">
-        <f t="shared" si="0"/>
+      <c r="AG6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="AI6" cm="1">
+        <f t="array" ref="AI6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="AJ6" cm="1">
+        <f t="array" ref="AJ6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>40</v>
+      </c>
+      <c r="AK6" cm="1">
+        <f t="array" ref="AK6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>40</v>
+      </c>
+      <c r="AL6" cm="1">
+        <f t="array" ref="AL6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>45</v>
+      </c>
+      <c r="AM6" cm="1">
+        <f t="array" ref="AM6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AN6" cm="1">
+        <f t="array" ref="AN6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>27</v>
+      </c>
+      <c r="AO6" cm="1">
+        <f t="array" ref="AO6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="AP6" cm="1">
+        <f t="array" ref="AP6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AQ6" cm="1">
+        <f t="array" ref="AQ6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>48</v>
+      </c>
+      <c r="AR6" cm="1">
+        <f t="array" ref="AR6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>26</v>
+      </c>
+      <c r="AS6" cm="1">
+        <f t="array" ref="AS6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>37</v>
+      </c>
+      <c r="AT6" cm="1">
+        <f t="array" ref="AT6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>36</v>
+      </c>
+      <c r="AU6" cm="1">
+        <f t="array" ref="AU6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AV6" cm="1">
+        <f t="array" ref="AV6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>39</v>
+      </c>
+      <c r="AW6" cm="1">
+        <f t="array" ref="AW6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AH6" cm="1">
-        <f t="array" ref="AH6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
-      <c r="AI6" cm="1">
-        <f t="array" ref="AI6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>40</v>
-      </c>
-      <c r="AJ6" cm="1">
-        <f t="array" ref="AJ6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>40</v>
-      </c>
-      <c r="AK6" cm="1">
-        <f t="array" ref="AK6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AX6" cm="1">
+        <f t="array" ref="AX6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AY6" cm="1">
+        <f t="array" ref="AY6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>46</v>
+      </c>
+      <c r="AZ6" cm="1">
+        <f t="array" ref="AZ6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>41</v>
+      </c>
+      <c r="BA6" cm="1">
+        <f t="array" ref="BA6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BB6" cm="1">
+        <f t="array" ref="BB6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AL6" cm="1">
-        <f t="array" ref="AL6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
-      <c r="AM6" cm="1">
-        <f t="array" ref="AM6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>27</v>
-      </c>
-      <c r="AN6" cm="1">
-        <f t="array" ref="AN6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>50</v>
-      </c>
-      <c r="AO6" cm="1">
-        <f t="array" ref="AO6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
-      <c r="AP6" cm="1">
-        <f t="array" ref="AP6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>48</v>
-      </c>
-      <c r="AQ6" cm="1">
-        <f t="array" ref="AQ6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BC6" cm="1">
+        <f t="array" ref="BC6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>33</v>
+      </c>
+      <c r="BD6" cm="1">
+        <f t="array" ref="BD6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BE6" cm="1">
+        <f t="array" ref="BE6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BF6" cm="1">
+        <f t="array" ref="BF6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="BG6" cm="1">
+        <f t="array" ref="BG6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BH6" cm="1">
+        <f t="array" ref="BH6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>41</v>
+      </c>
+      <c r="BI6" cm="1">
+        <f t="array" ref="BI6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AR6" cm="1">
-        <f t="array" ref="AR6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>37</v>
-      </c>
-      <c r="AS6" cm="1">
-        <f t="array" ref="AS6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>36</v>
-      </c>
-      <c r="AT6" cm="1">
-        <f t="array" ref="AT6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
-      <c r="AU6" cm="1">
-        <f t="array" ref="AU6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BJ6" cm="1">
+        <f t="array" ref="BJ6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="BK6" cm="1">
+        <f t="array" ref="BK6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BL6" cm="1">
+        <f t="array" ref="BL6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AV6" cm="1">
-        <f t="array" ref="AV6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BM6" cm="1">
+        <f t="array" ref="BM6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AE6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>45</v>
+      </c>
+      <c r="BN6" cm="1">
+        <f t="array" ref="BN6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AF6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="BO6" cm="1">
+        <f t="array" ref="BO6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AG6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>54</v>
+      </c>
+      <c r="BP6">
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="AW6" cm="1">
-        <f t="array" ref="AW6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
-      <c r="AX6" cm="1">
-        <f t="array" ref="AX6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>46</v>
-      </c>
-      <c r="AY6" cm="1">
-        <f t="array" ref="AY6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>41</v>
-      </c>
-      <c r="AZ6" cm="1">
-        <f t="array" ref="AZ6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
-      <c r="BA6" cm="1">
-        <f t="array" ref="BA6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>45</v>
-      </c>
-      <c r="BB6" cm="1">
-        <f t="array" ref="BB6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>33</v>
-      </c>
-      <c r="BC6" cm="1">
-        <f t="array" ref="BC6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="BD6" cm="1">
-        <f t="array" ref="BD6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
-      <c r="BE6" cm="1">
-        <f t="array" ref="BE6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
-      <c r="BF6" cm="1">
-        <f t="array" ref="BF6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
-      <c r="BG6" cm="1">
-        <f t="array" ref="BG6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>41</v>
-      </c>
-      <c r="BH6" cm="1">
-        <f t="array" ref="BH6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>26</v>
-      </c>
-      <c r="BI6" cm="1">
-        <f t="array" ref="BI6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
-      <c r="BJ6" cm="1">
-        <f t="array" ref="BJ6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="BK6" cm="1">
-        <f t="array" ref="BK6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>39</v>
-      </c>
-      <c r="BL6" cm="1">
-        <f t="array" ref="BL6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AE6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>45</v>
-      </c>
-      <c r="BM6" cm="1">
-        <f t="array" ref="BM6">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AF6, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
-      <c r="BO6">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="BR6">
+      <c r="BS6">
         <v>6</v>
       </c>
-      <c r="BS6" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH6:BN6)</f>
-        <v>43, 40, 40, 45, 52, 27, 50, 52, 48, 26, 37, 36, 34, 39, 32, 52, 46, 41, 52, 45, 33, 30, 34, 43, 52, 41, 26, 43, 30, 39, 45, 44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.3">
-      <c r="AG7">
-        <f t="shared" si="0"/>
+      <c r="BT6" t="str">
+        <f t="shared" si="0"/>
+        <v>43, 40, 40, 45, 52, 27, 50, 52, 48, 26, 37, 36, 34, 39, 32, 52, 46, 41, 52, 45, 33, 30, 34, 43, 52, 41, 26, 43, 30, 39, 45, 44, 54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="AH7">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BS7" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH7:BN7)</f>
+      <c r="BT7" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3424,129 +2905,129 @@
       <c r="Y8" t="s">
         <v>35</v>
       </c>
-      <c r="AG8">
-        <f t="shared" si="0"/>
+      <c r="AH8">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="AH8" cm="1">
-        <f t="array" ref="AH8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI8" cm="1">
+        <f t="array" ref="AI8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI8" cm="1">
-        <f t="array" ref="AI8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ8" cm="1">
+        <f t="array" ref="AJ8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AJ8" cm="1">
-        <f t="array" ref="AJ8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK8" cm="1">
+        <f t="array" ref="AK8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AK8" cm="1">
-        <f t="array" ref="AK8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL8" cm="1">
+        <f t="array" ref="AL8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AL8" cm="1">
-        <f t="array" ref="AL8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM8" cm="1">
+        <f t="array" ref="AM8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AM8" cm="1">
-        <f t="array" ref="AM8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AN8" cm="1">
+        <f t="array" ref="AN8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AN8" cm="1">
-        <f t="array" ref="AN8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO8" cm="1">
+        <f t="array" ref="AO8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AO8" cm="1">
-        <f t="array" ref="AO8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AP8" cm="1">
-        <f t="array" ref="AP8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AP8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AQ8" cm="1">
-        <f t="array" ref="AQ8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AQ8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AR8" cm="1">
+        <f t="array" ref="AR8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AR8" cm="1">
-        <f t="array" ref="AR8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AS8" cm="1">
+        <f t="array" ref="AS8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="AS8" cm="1">
-        <f t="array" ref="AS8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AT8" cm="1">
-        <f t="array" ref="AT8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AT8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>43</v>
       </c>
       <c r="AU8" cm="1">
-        <f t="array" ref="AU8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
+        <f t="array" ref="AU8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AV8" cm="1">
-        <f t="array" ref="AV8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AV8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AW8" cm="1">
+        <f t="array" ref="AW8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AW8" cm="1">
-        <f t="array" ref="AW8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AX8" cm="1">
+        <f t="array" ref="AX8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AX8" cm="1">
-        <f t="array" ref="AX8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AY8" cm="1">
-        <f t="array" ref="AY8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AY8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AZ8" cm="1">
+        <f t="array" ref="AZ8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AZ8" cm="1">
-        <f t="array" ref="AZ8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="BA8" cm="1">
-        <f t="array" ref="BA8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BA8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BB8" cm="1">
+        <f t="array" ref="BB8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="BB8" cm="1">
-        <f t="array" ref="BB8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="BC8" cm="1">
-        <f t="array" ref="BC8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BC8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BD8" cm="1">
+        <f t="array" ref="BD8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="BD8" cm="1">
-        <f t="array" ref="BD8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BE8" cm="1">
-        <f t="array" ref="BE8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="BE8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
       </c>
       <c r="BF8" cm="1">
-        <f t="array" ref="BF8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BF8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BG8" cm="1">
+        <f t="array" ref="BG8">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y8, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>31</v>
       </c>
-      <c r="BO8">
-        <f t="shared" si="1"/>
+      <c r="BP8">
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BP8" t="s">
+      <c r="BQ8" t="s">
         <v>62</v>
-      </c>
-      <c r="BQ8">
-        <v>1</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
-      <c r="BS8" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH8:BN8)</f>
+      <c r="BS8">
+        <v>1</v>
+      </c>
+      <c r="BT8" t="str">
+        <f t="shared" si="0"/>
         <v>0, 37, 37, 40, 28, 26, 45, 30, 52, 28, 46, 43, 43, 30, 39, 45, 52, 41, 34, 49, 30, 37, 52, 34, 31</v>
       </c>
     </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -3637,143 +3118,143 @@
       <c r="AD9" t="s">
         <v>48</v>
       </c>
-      <c r="AG9">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AH9" cm="1">
-        <f t="array" ref="AH9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AH9">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI9" cm="1">
+        <f t="array" ref="AI9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AI9" cm="1">
-        <f t="array" ref="AI9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AJ9" cm="1">
-        <f t="array" ref="AJ9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="AJ9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AK9" cm="1">
-        <f t="array" ref="AK9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AK9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AL9" cm="1">
+        <f t="array" ref="AL9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AL9" cm="1">
-        <f t="array" ref="AL9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM9" cm="1">
+        <f t="array" ref="AM9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AM9" cm="1">
-        <f t="array" ref="AM9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AN9" cm="1">
+        <f t="array" ref="AN9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AN9" cm="1">
-        <f t="array" ref="AN9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO9" cm="1">
+        <f t="array" ref="AO9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AO9" cm="1">
-        <f t="array" ref="AO9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP9" cm="1">
+        <f t="array" ref="AP9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="AP9" cm="1">
-        <f t="array" ref="AP9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AQ9" cm="1">
-        <f t="array" ref="AQ9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="AQ9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AR9" cm="1">
-        <f t="array" ref="AR9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AR9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="AS9" cm="1">
-        <f t="array" ref="AS9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AT9" cm="1">
+        <f t="array" ref="AT9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AT9" cm="1">
-        <f t="array" ref="AT9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AU9" cm="1">
+        <f t="array" ref="AU9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AU9" cm="1">
-        <f t="array" ref="AU9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AV9" cm="1">
+        <f t="array" ref="AV9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>47</v>
       </c>
-      <c r="AV9" cm="1">
-        <f t="array" ref="AV9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AW9" cm="1">
-        <f t="array" ref="AW9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AW9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AX9" cm="1">
-        <f t="array" ref="AX9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AY9" cm="1">
+        <f t="array" ref="AY9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AY9" cm="1">
-        <f t="array" ref="AY9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AZ9" cm="1">
+        <f t="array" ref="AZ9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AZ9" cm="1">
-        <f t="array" ref="AZ9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BA9" cm="1">
-        <f t="array" ref="BA9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
+        <f t="array" ref="BA9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
       </c>
       <c r="BB9" cm="1">
-        <f t="array" ref="BB9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BB9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="BC9" cm="1">
+        <f t="array" ref="BC9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BC9" cm="1">
-        <f t="array" ref="BC9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BD9" cm="1">
+        <f t="array" ref="BD9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BD9" cm="1">
-        <f t="array" ref="BD9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BE9" cm="1">
+        <f t="array" ref="BE9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BE9" cm="1">
-        <f t="array" ref="BE9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="BF9" cm="1">
-        <f t="array" ref="BF9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BF9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="BG9" cm="1">
+        <f t="array" ref="BG9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>55</v>
       </c>
-      <c r="BG9" cm="1">
-        <f t="array" ref="BG9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="BH9" cm="1">
-        <f t="array" ref="BH9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BH9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BI9" cm="1">
+        <f t="array" ref="BI9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BI9" cm="1">
-        <f t="array" ref="BI9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BJ9" cm="1">
-        <f t="array" ref="BJ9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="BJ9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
       </c>
       <c r="BK9" cm="1">
-        <f t="array" ref="BK9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
-      <c r="BO9">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="BR9">
+        <f t="array" ref="BK9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BL9" cm="1">
+        <f t="array" ref="BL9">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD9, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="BP9">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="BS9">
         <v>2</v>
       </c>
-      <c r="BS9" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH9:BN9)</f>
+      <c r="BT9" t="str">
+        <f t="shared" si="0"/>
         <v>39, 30, 34, 32, 33, 27, 40, 46, 43, 44, 52, 33, 26, 47, 30, 52, 39, 40, 52, 43, 40, 40, 45, 44, 55, 34, 45, 52, 34, 44</v>
       </c>
     </row>
-    <row r="10" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -3825,91 +3306,91 @@
       <c r="Q10" t="s">
         <v>58</v>
       </c>
-      <c r="AG10">
-        <f t="shared" si="0"/>
+      <c r="AH10">
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="AH10" cm="1">
-        <f t="array" ref="AH10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI10" cm="1">
+        <f t="array" ref="AI10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AI10" cm="1">
-        <f t="array" ref="AI10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AJ10" cm="1">
-        <f t="array" ref="AJ10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AJ10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AK10" cm="1">
+        <f t="array" ref="AK10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AK10" cm="1">
-        <f t="array" ref="AK10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AL10" cm="1">
-        <f t="array" ref="AL10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AL10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AM10" cm="1">
+        <f t="array" ref="AM10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>48</v>
       </c>
-      <c r="AM10" cm="1">
-        <f t="array" ref="AM10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AN10" cm="1">
-        <f t="array" ref="AN10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AN10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AO10" cm="1">
+        <f t="array" ref="AO10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AO10" cm="1">
-        <f t="array" ref="AO10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP10" cm="1">
+        <f t="array" ref="AP10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AP10" cm="1">
-        <f t="array" ref="AP10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ10" cm="1">
+        <f t="array" ref="AQ10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AQ10" cm="1">
-        <f t="array" ref="AQ10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR10" cm="1">
+        <f t="array" ref="AR10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AR10" cm="1">
-        <f t="array" ref="AR10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AS10" cm="1">
+        <f t="array" ref="AS10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AS10" cm="1">
-        <f t="array" ref="AS10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AT10" cm="1">
+        <f t="array" ref="AT10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AT10" cm="1">
-        <f t="array" ref="AT10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AU10" cm="1">
-        <f t="array" ref="AU10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AU10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AV10" cm="1">
+        <f t="array" ref="AV10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AV10" cm="1">
-        <f t="array" ref="AV10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AW10" cm="1">
+        <f t="array" ref="AW10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AW10" cm="1">
-        <f t="array" ref="AW10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>56</v>
-      </c>
       <c r="AX10" cm="1">
-        <f t="array" ref="AX10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>56</v>
+      </c>
+      <c r="AY10" cm="1">
+        <f t="array" ref="AY10">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q10, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="BO10">
-        <f t="shared" si="1"/>
+      <c r="BP10">
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="BR10">
+      <c r="BS10">
         <v>3</v>
       </c>
-      <c r="BS10" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH10:BN10)</f>
+      <c r="BT10" t="str">
+        <f t="shared" si="0"/>
         <v>26, 52, 39, 30, 48, 52, 28, 40, 38, 41, 40, 39, 30, 39, 45, 56, 54</v>
       </c>
     </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -3985,126 +3466,126 @@
       <c r="Y11" t="s">
         <v>36</v>
       </c>
-      <c r="AG11">
-        <f t="shared" si="0"/>
+      <c r="AH11">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="AH11" cm="1">
-        <f t="array" ref="AH11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI11" cm="1">
+        <f t="array" ref="AI11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="AI11" cm="1">
-        <f t="array" ref="AI11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ11" cm="1">
+        <f t="array" ref="AJ11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AJ11" cm="1">
-        <f t="array" ref="AJ11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="AK11" cm="1">
-        <f t="array" ref="AK11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
+        <f t="array" ref="AK11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="AL11" cm="1">
-        <f t="array" ref="AL11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AL11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AM11" cm="1">
+        <f t="array" ref="AM11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AM11" cm="1">
-        <f t="array" ref="AM11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AN11" cm="1">
-        <f t="array" ref="AN11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AN11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AO11" cm="1">
+        <f t="array" ref="AO11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AO11" cm="1">
-        <f t="array" ref="AO11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AP11" cm="1">
-        <f t="array" ref="AP11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AP11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AQ11" cm="1">
+        <f t="array" ref="AQ11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AQ11" cm="1">
-        <f t="array" ref="AQ11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR11" cm="1">
+        <f t="array" ref="AR11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>36</v>
       </c>
-      <c r="AR11" cm="1">
-        <f t="array" ref="AR11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AS11" cm="1">
-        <f t="array" ref="AS11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AT11" cm="1">
+        <f t="array" ref="AT11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AT11" cm="1">
-        <f t="array" ref="AT11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AU11" cm="1">
-        <f t="array" ref="AU11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AU11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AV11" cm="1">
+        <f t="array" ref="AV11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AV11" cm="1">
-        <f t="array" ref="AV11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AW11" cm="1">
-        <f t="array" ref="AW11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="AW11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AX11" cm="1">
-        <f t="array" ref="AX11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AY11" cm="1">
+        <f t="array" ref="AY11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AY11" cm="1">
-        <f t="array" ref="AY11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AZ11" cm="1">
+        <f t="array" ref="AZ11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AZ11" cm="1">
-        <f t="array" ref="AZ11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BA11" cm="1">
+        <f t="array" ref="BA11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="BA11" cm="1">
-        <f t="array" ref="BA11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BB11" cm="1">
+        <f t="array" ref="BB11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BB11" cm="1">
-        <f t="array" ref="BB11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BC11" cm="1">
+        <f t="array" ref="BC11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="BC11" cm="1">
-        <f t="array" ref="BC11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="BD11" cm="1">
-        <f t="array" ref="BD11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="BD11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="BE11" cm="1">
-        <f t="array" ref="BE11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BE11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BF11" cm="1">
+        <f t="array" ref="BF11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BF11" cm="1">
-        <f t="array" ref="BF11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BG11" cm="1">
+        <f t="array" ref="BG11">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y11, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="BO11">
-        <f t="shared" si="1"/>
+      <c r="BP11">
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BQ11">
+      <c r="BR11">
         <v>2</v>
       </c>
-      <c r="BR11">
+      <c r="BS11">
         <v>4</v>
       </c>
-      <c r="BS11" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH11:BN11)</f>
+      <c r="BT11" t="str">
+        <f t="shared" si="0"/>
         <v>4, 37, 44, 30, 53, 52, 41, 34, 28, 36, 52, 26, 52, 39, 30, 34, 32, 33, 27, 40, 46, 43, 34, 39, 32</v>
       </c>
     </row>
-    <row r="12" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -4177,119 +3658,119 @@
       <c r="X12" t="s">
         <v>44</v>
       </c>
-      <c r="AG12">
-        <f t="shared" si="0"/>
+      <c r="AH12">
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="AH12" cm="1">
-        <f t="array" ref="AH12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI12" cm="1">
+        <f t="array" ref="AI12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AI12" cm="1">
-        <f t="array" ref="AI12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ12" cm="1">
+        <f t="array" ref="AJ12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AJ12" cm="1">
-        <f t="array" ref="AJ12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK12" cm="1">
+        <f t="array" ref="AK12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AK12" cm="1">
-        <f t="array" ref="AK12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL12" cm="1">
+        <f t="array" ref="AL12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AL12" cm="1">
-        <f t="array" ref="AL12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM12" cm="1">
+        <f t="array" ref="AM12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AM12" cm="1">
-        <f t="array" ref="AM12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AN12" cm="1">
+        <f t="array" ref="AN12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AN12" cm="1">
-        <f t="array" ref="AN12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AO12" cm="1">
-        <f t="array" ref="AO12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AO12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AP12" cm="1">
+        <f t="array" ref="AP12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AP12" cm="1">
-        <f t="array" ref="AP12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ12" cm="1">
+        <f t="array" ref="AQ12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AQ12" cm="1">
-        <f t="array" ref="AQ12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AR12" cm="1">
-        <f t="array" ref="AR12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AR12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AS12" cm="1">
+        <f t="array" ref="AS12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AS12" cm="1">
-        <f t="array" ref="AS12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AT12" cm="1">
+        <f t="array" ref="AT12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AT12" cm="1">
-        <f t="array" ref="AT12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AU12" cm="1">
+        <f t="array" ref="AU12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AU12" cm="1">
-        <f t="array" ref="AU12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AV12" cm="1">
-        <f t="array" ref="AV12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AV12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AW12" cm="1">
+        <f t="array" ref="AW12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="AW12" cm="1">
-        <f t="array" ref="AW12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AX12" cm="1">
+        <f t="array" ref="AX12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AX12" cm="1">
-        <f t="array" ref="AX12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AY12" cm="1">
-        <f t="array" ref="AY12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AY12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AZ12" cm="1">
+        <f t="array" ref="AZ12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AZ12" cm="1">
-        <f t="array" ref="AZ12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BA12" cm="1">
+        <f t="array" ref="BA12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BA12" cm="1">
-        <f t="array" ref="BA12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BB12" cm="1">
-        <f t="array" ref="BB12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="BB12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
       </c>
       <c r="BC12" cm="1">
-        <f t="array" ref="BC12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BC12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BD12" cm="1">
+        <f t="array" ref="BD12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BD12" cm="1">
-        <f t="array" ref="BD12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BE12" cm="1">
+        <f t="array" ref="BE12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BE12" cm="1">
-        <f t="array" ref="BE12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BF12" cm="1">
+        <f t="array" ref="BF12">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X12, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BO12">
-        <f t="shared" si="1"/>
+      <c r="BP12">
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="BR12">
+      <c r="BS12">
         <v>5</v>
       </c>
-      <c r="BS12" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH12:BN12)</f>
+      <c r="BT12" t="str">
+        <f t="shared" si="0"/>
         <v>28, 40, 38, 41, 40, 39, 30, 39, 45, 52, 26, 39, 29, 52, 46, 39, 34, 40, 39, 52, 34, 39, 45, 40</v>
       </c>
     </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -4332,89 +3813,89 @@
       <c r="N13" t="s">
         <v>58</v>
       </c>
-      <c r="AG13">
-        <f t="shared" si="0"/>
+      <c r="AH13">
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="AH13" cm="1">
-        <f t="array" ref="AH13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI13" cm="1">
+        <f t="array" ref="AI13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AI13" cm="1">
-        <f t="array" ref="AI13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ13" cm="1">
+        <f t="array" ref="AJ13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AJ13" cm="1">
-        <f t="array" ref="AJ13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AK13" cm="1">
-        <f t="array" ref="AK13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AK13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AL13" cm="1">
-        <f t="array" ref="AL13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AL13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AM13" cm="1">
+        <f t="array" ref="AM13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AM13" cm="1">
-        <f t="array" ref="AM13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AN13" cm="1">
+        <f t="array" ref="AN13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AN13" cm="1">
-        <f t="array" ref="AN13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO13" cm="1">
+        <f t="array" ref="AO13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AO13" cm="1">
-        <f t="array" ref="AO13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP13" cm="1">
+        <f t="array" ref="AP13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AP13" cm="1">
-        <f t="array" ref="AP13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ13" cm="1">
+        <f t="array" ref="AQ13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AQ13" cm="1">
-        <f t="array" ref="AQ13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR13" cm="1">
+        <f t="array" ref="AR13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AR13" cm="1">
-        <f t="array" ref="AR13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AS13" cm="1">
-        <f t="array" ref="AS13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AT13" cm="1">
+        <f t="array" ref="AT13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AT13" cm="1">
-        <f t="array" ref="AT13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AU13" cm="1">
+        <f t="array" ref="AU13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AU13" cm="1">
-        <f t="array" ref="AU13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AV13" cm="1">
+        <f t="array" ref="AV13">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N13, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="BO13">
-        <f t="shared" si="1"/>
+      <c r="BP13">
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="BR13">
+      <c r="BS13">
         <v>6</v>
       </c>
-      <c r="BS13" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH13:BN13)</f>
+      <c r="BT13" t="str">
+        <f t="shared" si="0"/>
         <v>40, 39, 30, 52, 28, 40, 38, 41, 40, 39, 30, 39, 45, 54</v>
       </c>
     </row>
-    <row r="14" spans="1:71" x14ac:dyDescent="0.3">
-      <c r="AG14">
-        <f t="shared" si="0"/>
+    <row r="14" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="AH14">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BS14" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH14:BN14)</f>
+      <c r="BT14" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -4481,117 +3962,117 @@
       <c r="V15" t="s">
         <v>43</v>
       </c>
-      <c r="AG15">
-        <f t="shared" si="0"/>
+      <c r="AH15">
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="AH15" cm="1">
-        <f t="array" ref="AH15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI15" cm="1">
+        <f t="array" ref="AI15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI15" cm="1">
-        <f t="array" ref="AI15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="AJ15" cm="1">
-        <f t="array" ref="AJ15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AJ15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="AK15" cm="1">
-        <f t="array" ref="AK15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AK15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AL15" cm="1">
+        <f t="array" ref="AL15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>31</v>
       </c>
-      <c r="AL15" cm="1">
-        <f t="array" ref="AL15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AM15" cm="1">
-        <f t="array" ref="AM15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="AN15" cm="1">
+        <f t="array" ref="AN15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AN15" cm="1">
-        <f t="array" ref="AN15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO15" cm="1">
+        <f t="array" ref="AO15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AO15" cm="1">
-        <f t="array" ref="AO15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AP15" cm="1">
-        <f t="array" ref="AP15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AP15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AQ15" cm="1">
-        <f t="array" ref="AQ15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AQ15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AR15" cm="1">
+        <f t="array" ref="AR15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AR15" cm="1">
-        <f t="array" ref="AR15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AS15" cm="1">
+        <f t="array" ref="AS15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="AS15" cm="1">
-        <f t="array" ref="AS15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AT15" cm="1">
-        <f t="array" ref="AT15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AT15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AU15" cm="1">
+        <f t="array" ref="AU15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AU15" cm="1">
-        <f t="array" ref="AU15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AV15" cm="1">
+        <f t="array" ref="AV15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AV15" cm="1">
-        <f t="array" ref="AV15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="AW15" cm="1">
-        <f t="array" ref="AW15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AW15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="AX15" cm="1">
+        <f t="array" ref="AX15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AX15" cm="1">
-        <f t="array" ref="AX15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AY15" cm="1">
-        <f t="array" ref="AY15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AY15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AZ15" cm="1">
+        <f t="array" ref="AZ15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="AZ15" cm="1">
-        <f t="array" ref="AZ15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BA15" cm="1">
+        <f t="array" ref="BA15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BA15" cm="1">
-        <f t="array" ref="BA15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="BB15" cm="1">
-        <f t="array" ref="BB15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BB15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BC15" cm="1">
+        <f t="array" ref="BC15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BC15" cm="1">
-        <f t="array" ref="BC15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BD15" cm="1">
+        <f t="array" ref="BD15">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V15, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BO15">
-        <f t="shared" si="1"/>
+      <c r="BP15">
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="BP15" t="s">
+      <c r="BQ15" t="s">
         <v>63</v>
-      </c>
-      <c r="BQ15">
-        <v>1</v>
       </c>
       <c r="BR15">
         <v>1</v>
       </c>
-      <c r="BS15" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH15:BN15)</f>
+      <c r="BS15">
+        <v>1</v>
+      </c>
+      <c r="BT15" t="str">
+        <f t="shared" si="0"/>
         <v>0, 44, 52, 31, 43, 26, 38, 30, 52, 27, 46, 34, 37, 29, 44, 53, 52, 46, 39, 34, 40, 39</v>
       </c>
     </row>
-    <row r="16" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -4649,99 +4130,99 @@
       <c r="S16" t="s">
         <v>52</v>
       </c>
-      <c r="AG16">
-        <f t="shared" si="0"/>
+      <c r="AH16">
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="AH16" cm="1">
-        <f t="array" ref="AH16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI16" cm="1">
+        <f t="array" ref="AI16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AI16" cm="1">
-        <f t="array" ref="AI16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AJ16" cm="1">
-        <f t="array" ref="AJ16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="AJ16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AK16" cm="1">
-        <f t="array" ref="AK16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AK16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AL16" cm="1">
+        <f t="array" ref="AL16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AL16" cm="1">
-        <f t="array" ref="AL16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM16" cm="1">
+        <f t="array" ref="AM16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AM16" cm="1">
-        <f t="array" ref="AM16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AN16" cm="1">
+        <f t="array" ref="AN16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AN16" cm="1">
-        <f t="array" ref="AN16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO16" cm="1">
+        <f t="array" ref="AO16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AO16" cm="1">
-        <f t="array" ref="AO16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP16" cm="1">
+        <f t="array" ref="AP16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="AP16" cm="1">
-        <f t="array" ref="AP16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AQ16" cm="1">
-        <f t="array" ref="AQ16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="AQ16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AR16" cm="1">
-        <f t="array" ref="AR16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AR16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="AS16" cm="1">
-        <f t="array" ref="AS16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AT16" cm="1">
+        <f t="array" ref="AT16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AT16" cm="1">
-        <f t="array" ref="AT16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AU16" cm="1">
+        <f t="array" ref="AU16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AU16" cm="1">
-        <f t="array" ref="AU16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AV16" cm="1">
+        <f t="array" ref="AV16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AV16" cm="1">
-        <f t="array" ref="AV16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AW16" cm="1">
-        <f t="array" ref="AW16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AW16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AX16" cm="1">
+        <f t="array" ref="AX16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AX16" cm="1">
-        <f t="array" ref="AX16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AY16" cm="1">
-        <f t="array" ref="AY16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AY16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="AZ16" cm="1">
+        <f t="array" ref="AZ16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AZ16" cm="1">
-        <f t="array" ref="AZ16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BA16" cm="1">
+        <f t="array" ref="BA16">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S16, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>48</v>
       </c>
-      <c r="BO16">
-        <f t="shared" si="1"/>
+      <c r="BP16">
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="BR16">
+      <c r="BS16">
         <v>2</v>
       </c>
-      <c r="BS16" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH16:BN16)</f>
+      <c r="BT16" t="str">
+        <f t="shared" si="0"/>
         <v>39, 30, 34, 32, 33, 27, 40, 46, 43, 44, 52, 26, 39, 29, 52, 32, 43, 40, 48</v>
       </c>
     </row>
-    <row r="17" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -4775,67 +4256,67 @@
       <c r="K17" t="s">
         <v>58</v>
       </c>
-      <c r="AG17">
-        <f t="shared" si="0"/>
+      <c r="AH17">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="AH17" cm="1">
-        <f t="array" ref="AH17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI17" cm="1">
+        <f t="array" ref="AI17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AI17" cm="1">
-        <f t="array" ref="AI17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ17" cm="1">
+        <f t="array" ref="AJ17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AJ17" cm="1">
-        <f t="array" ref="AJ17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK17" cm="1">
+        <f t="array" ref="AK17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AK17" cm="1">
-        <f t="array" ref="AK17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL17" cm="1">
+        <f t="array" ref="AL17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AL17" cm="1">
-        <f t="array" ref="AL17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM17" cm="1">
+        <f t="array" ref="AM17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AM17" cm="1">
-        <f t="array" ref="AM17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AN17" cm="1">
+        <f t="array" ref="AN17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AN17" cm="1">
-        <f t="array" ref="AN17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AO17" cm="1">
-        <f t="array" ref="AO17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AO17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AP17" cm="1">
+        <f t="array" ref="AP17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AP17" cm="1">
-        <f t="array" ref="AP17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ17" cm="1">
+        <f t="array" ref="AQ17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AQ17" cm="1">
-        <f t="array" ref="AQ17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="AR17" cm="1">
-        <f t="array" ref="AR17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AR17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="AS17" cm="1">
+        <f t="array" ref="AS17">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K17, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="BO17">
-        <f t="shared" si="1"/>
+      <c r="BP17">
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="BR17">
+      <c r="BS17">
         <v>3</v>
       </c>
-      <c r="BS17" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH17:BN17)</f>
+      <c r="BT17" t="str">
+        <f t="shared" si="0"/>
         <v>28, 40, 38, 41, 40, 39, 30, 39, 45, 44, 54</v>
       </c>
     </row>
-    <row r="18" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -4929,150 +4410,150 @@
       <c r="AE18" t="s">
         <v>36</v>
       </c>
-      <c r="AG18">
-        <f t="shared" si="0"/>
+      <c r="AH18">
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="AH18" cm="1">
-        <f t="array" ref="AH18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI18" cm="1">
+        <f t="array" ref="AI18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>4</v>
       </c>
-      <c r="AI18" cm="1">
-        <f t="array" ref="AI18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ18" cm="1">
+        <f t="array" ref="AJ18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AJ18" cm="1">
-        <f t="array" ref="AJ18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK18" cm="1">
+        <f t="array" ref="AK18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AK18" cm="1">
-        <f t="array" ref="AK18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL18" cm="1">
+        <f t="array" ref="AL18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AL18" cm="1">
-        <f t="array" ref="AL18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AM18" cm="1">
-        <f t="array" ref="AM18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AN18" cm="1">
+        <f t="array" ref="AN18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AN18" cm="1">
-        <f t="array" ref="AN18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO18" cm="1">
+        <f t="array" ref="AO18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AO18" cm="1">
-        <f t="array" ref="AO18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP18" cm="1">
+        <f t="array" ref="AP18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AP18" cm="1">
-        <f t="array" ref="AP18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ18" cm="1">
+        <f t="array" ref="AQ18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AQ18" cm="1">
-        <f t="array" ref="AQ18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR18" cm="1">
+        <f t="array" ref="AR18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AR18" cm="1">
-        <f t="array" ref="AR18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AS18" cm="1">
+        <f t="array" ref="AS18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AS18" cm="1">
-        <f t="array" ref="AS18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AT18" cm="1">
-        <f t="array" ref="AT18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AT18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AU18" cm="1">
+        <f t="array" ref="AU18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AU18" cm="1">
-        <f t="array" ref="AU18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AV18" cm="1">
+        <f t="array" ref="AV18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AV18" cm="1">
-        <f t="array" ref="AV18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AW18" cm="1">
-        <f t="array" ref="AW18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="AW18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
       </c>
       <c r="AX18" cm="1">
-        <f t="array" ref="AX18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="AY18" cm="1">
+        <f t="array" ref="AY18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AY18" cm="1">
-        <f t="array" ref="AY18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AZ18" cm="1">
+        <f t="array" ref="AZ18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AZ18" cm="1">
-        <f t="array" ref="AZ18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="BA18" cm="1">
-        <f t="array" ref="BA18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
+        <f t="array" ref="BA18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="BB18" cm="1">
-        <f t="array" ref="BB18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="BB18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="BC18" cm="1">
-        <f t="array" ref="BC18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="BC18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="BD18" cm="1">
-        <f t="array" ref="BD18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BD18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BE18" cm="1">
+        <f t="array" ref="BE18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BE18" cm="1">
-        <f t="array" ref="BE18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BF18" cm="1">
-        <f t="array" ref="BF18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
+        <f t="array" ref="BF18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
       </c>
       <c r="BG18" cm="1">
-        <f t="array" ref="BG18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z18, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>46</v>
-      </c>
-      <c r="BH18" cm="1">
-        <f t="array" ref="BH18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA18, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>39</v>
-      </c>
-      <c r="BI18" cm="1">
-        <f t="array" ref="BI18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB18, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>39</v>
-      </c>
-      <c r="BJ18" cm="1">
-        <f t="array" ref="BJ18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC18, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
-      <c r="BK18" cm="1">
-        <f t="array" ref="BK18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD18, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>39</v>
-      </c>
-      <c r="BL18" cm="1">
-        <f t="array" ref="BL18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AE18, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>32</v>
-      </c>
-      <c r="BO18">
-        <f t="shared" si="1"/>
+        <f t="array" ref="BG18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y18, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="BH18" t="e" cm="1">
+        <f t="array" ref="BH18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z18,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BI18" t="e" cm="1">
+        <f t="array" ref="BI18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA18,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BJ18" t="e" cm="1">
+        <f t="array" ref="BJ18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB18,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BK18" t="e" cm="1">
+        <f t="array" ref="BK18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC18,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BL18" t="e" cm="1">
+        <f t="array" ref="BL18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD18,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BM18" t="e" cm="1">
+        <f t="array" ref="BM18">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AE18,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BP18">
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BQ18">
+      <c r="BR18">
         <v>2</v>
       </c>
-      <c r="BR18">
+      <c r="BS18">
         <v>4</v>
       </c>
-      <c r="BS18" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH18:BN18)</f>
-        <v>4, 26, 28, 33, 52, 28, 40, 38, 41, 40, 39, 30, 39, 45, 52, 44, 45, 40, 43, 30, 44, 52, 26, 52, 43, 46, 39, 39, 34, 39, 32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="BT18" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -5157,135 +4638,135 @@
       <c r="AB19" t="s">
         <v>54</v>
       </c>
-      <c r="AG19">
-        <f t="shared" si="0"/>
+      <c r="AH19">
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="AH19" cm="1">
-        <f t="array" ref="AH19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI19" cm="1">
+        <f t="array" ref="AI19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AI19" cm="1">
-        <f t="array" ref="AI19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AJ19" cm="1">
-        <f t="array" ref="AJ19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
+        <f t="array" ref="AJ19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AK19" cm="1">
-        <f t="array" ref="AK19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AK19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AL19" cm="1">
+        <f t="array" ref="AL19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AL19" cm="1">
-        <f t="array" ref="AL19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AM19" cm="1">
-        <f t="array" ref="AM19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AN19" cm="1">
+        <f t="array" ref="AN19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AN19" cm="1">
-        <f t="array" ref="AN19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO19" cm="1">
+        <f t="array" ref="AO19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AO19" cm="1">
-        <f t="array" ref="AO19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP19" cm="1">
+        <f t="array" ref="AP19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="AP19" cm="1">
-        <f t="array" ref="AP19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ19" cm="1">
+        <f t="array" ref="AQ19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AQ19" cm="1">
-        <f t="array" ref="AQ19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR19" cm="1">
+        <f t="array" ref="AR19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AR19" cm="1">
-        <f t="array" ref="AR19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AS19" cm="1">
-        <f t="array" ref="AS19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AT19" cm="1">
+        <f t="array" ref="AT19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AT19" cm="1">
-        <f t="array" ref="AT19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AU19" cm="1">
+        <f t="array" ref="AU19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AU19" cm="1">
-        <f t="array" ref="AU19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AV19" cm="1">
+        <f t="array" ref="AV19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AV19" cm="1">
-        <f t="array" ref="AV19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AW19" cm="1">
-        <f t="array" ref="AW19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AW19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AX19" cm="1">
+        <f t="array" ref="AX19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AX19" cm="1">
-        <f t="array" ref="AX19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AY19" cm="1">
-        <f t="array" ref="AY19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AY19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AZ19" cm="1">
+        <f t="array" ref="AZ19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AZ19" cm="1">
-        <f t="array" ref="AZ19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BA19" cm="1">
+        <f t="array" ref="BA19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="BA19" cm="1">
-        <f t="array" ref="BA19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BB19" cm="1">
-        <f t="array" ref="BB19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BB19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BC19" cm="1">
+        <f t="array" ref="BC19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="BC19" cm="1">
-        <f t="array" ref="BC19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BD19" cm="1">
+        <f t="array" ref="BD19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BD19" cm="1">
-        <f t="array" ref="BD19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BE19" cm="1">
+        <f t="array" ref="BE19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="BE19" cm="1">
-        <f t="array" ref="BE19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BF19" cm="1">
-        <f t="array" ref="BF19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BF19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BG19" cm="1">
+        <f t="array" ref="BG19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y19, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="BG19" cm="1">
-        <f t="array" ref="BG19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z19, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>53</v>
-      </c>
-      <c r="BH19" cm="1">
-        <f t="array" ref="BH19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA19, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
-      <c r="BI19" cm="1">
-        <f t="array" ref="BI19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB19, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>50</v>
-      </c>
-      <c r="BO19">
-        <f t="shared" si="1"/>
+      <c r="BH19" t="e" cm="1">
+        <f t="array" ref="BH19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z19,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BI19" t="e" cm="1">
+        <f t="array" ref="BI19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA19,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BJ19" t="e" cm="1">
+        <f t="array" ref="BJ19">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB19,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BP19">
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="BR19">
+      <c r="BS19">
         <v>5</v>
       </c>
-      <c r="BS19" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH19:BN19)</f>
-        <v>26, 43, 30, 26, 52, 28, 40, 46, 39, 45, 52, 26, 39, 29, 52, 38, 34, 39, 53, 52, 38, 26, 49, 52, 49, 53, 52, 50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="BT19" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -5343,109 +4824,109 @@
       <c r="S20" t="s">
         <v>58</v>
       </c>
-      <c r="AG20">
-        <f t="shared" si="0"/>
+      <c r="AH20">
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="AH20" cm="1">
-        <f t="array" ref="AH20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI20" cm="1">
+        <f t="array" ref="AI20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>31</v>
       </c>
-      <c r="AI20" cm="1">
-        <f t="array" ref="AI20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ20" cm="1">
+        <f t="array" ref="AJ20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AJ20" cm="1">
-        <f t="array" ref="AJ20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AK20" cm="1">
-        <f t="array" ref="AK20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AK20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AL20" cm="1">
-        <f t="array" ref="AL20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AL20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AM20" cm="1">
+        <f t="array" ref="AM20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AM20" cm="1">
-        <f t="array" ref="AM20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AN20" cm="1">
+        <f t="array" ref="AN20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AN20" cm="1">
-        <f t="array" ref="AN20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO20" cm="1">
+        <f t="array" ref="AO20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="AO20" cm="1">
-        <f t="array" ref="AO20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP20" cm="1">
+        <f t="array" ref="AP20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AP20" cm="1">
-        <f t="array" ref="AP20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ20" cm="1">
+        <f t="array" ref="AQ20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AQ20" cm="1">
-        <f t="array" ref="AQ20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AR20" cm="1">
-        <f t="array" ref="AR20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AR20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AS20" cm="1">
+        <f t="array" ref="AS20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AS20" cm="1">
-        <f t="array" ref="AS20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AT20" cm="1">
+        <f t="array" ref="AT20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AT20" cm="1">
-        <f t="array" ref="AT20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AU20" cm="1">
-        <f t="array" ref="AU20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AU20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AV20" cm="1">
+        <f t="array" ref="AV20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AV20" cm="1">
-        <f t="array" ref="AV20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AW20" cm="1">
+        <f t="array" ref="AW20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AW20" cm="1">
-        <f t="array" ref="AW20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AX20" cm="1">
+        <f t="array" ref="AX20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="AX20" cm="1">
-        <f t="array" ref="AX20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AY20" cm="1">
-        <f t="array" ref="AY20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="AY20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AZ20" cm="1">
-        <f t="array" ref="AZ20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AZ20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="BA20" cm="1">
+        <f t="array" ref="BA20">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S20, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="BO20">
-        <f t="shared" si="1"/>
+      <c r="BP20">
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="BR20">
+      <c r="BS20">
         <v>6</v>
       </c>
-      <c r="BS20" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH20:BN20)</f>
+      <c r="BT20" t="str">
+        <f t="shared" si="0"/>
         <v>31, 40, 43, 52, 27, 40, 46, 39, 29, 34, 39, 32, 52, 27, 40, 49, 30, 44, 54</v>
       </c>
     </row>
-    <row r="21" spans="1:71" x14ac:dyDescent="0.3">
-      <c r="AG21">
-        <f t="shared" si="0"/>
+    <row r="21" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="AH21">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BS21" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH21:BN21)</f>
+      <c r="BT21" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -5539,153 +5020,153 @@
       <c r="AE22" t="s">
         <v>34</v>
       </c>
-      <c r="AG22">
-        <f t="shared" si="0"/>
+      <c r="AH22">
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="AH22" cm="1">
-        <f t="array" ref="AH22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI22" cm="1">
+        <f t="array" ref="AI22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>17</v>
       </c>
-      <c r="AI22" cm="1">
-        <f t="array" ref="AI22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AJ22" cm="1">
-        <f t="array" ref="AJ22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AJ22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AK22" cm="1">
+        <f t="array" ref="AK22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AK22" cm="1">
-        <f t="array" ref="AK22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL22" cm="1">
+        <f t="array" ref="AL22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AL22" cm="1">
-        <f t="array" ref="AL22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM22" cm="1">
+        <f t="array" ref="AM22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>47</v>
       </c>
-      <c r="AM22" cm="1">
-        <f t="array" ref="AM22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AN22" cm="1">
-        <f t="array" ref="AN22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AN22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AO22" cm="1">
-        <f t="array" ref="AO22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AO22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AP22" cm="1">
+        <f t="array" ref="AP22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AP22" cm="1">
-        <f t="array" ref="AP22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AQ22" cm="1">
-        <f t="array" ref="AQ22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AQ22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AR22" cm="1">
+        <f t="array" ref="AR22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AR22" cm="1">
-        <f t="array" ref="AR22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AS22" cm="1">
+        <f t="array" ref="AS22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>50</v>
       </c>
-      <c r="AS22" cm="1">
-        <f t="array" ref="AS22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AT22" cm="1">
-        <f t="array" ref="AT22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AT22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AU22" cm="1">
+        <f t="array" ref="AU22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AU22" cm="1">
-        <f t="array" ref="AU22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AV22" cm="1">
+        <f t="array" ref="AV22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AV22" cm="1">
-        <f t="array" ref="AV22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AW22" cm="1">
+        <f t="array" ref="AW22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AW22" cm="1">
-        <f t="array" ref="AW22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AX22" cm="1">
+        <f t="array" ref="AX22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AX22" cm="1">
-        <f t="array" ref="AX22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AY22" cm="1">
+        <f t="array" ref="AY22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AY22" cm="1">
-        <f t="array" ref="AY22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AZ22" cm="1">
+        <f t="array" ref="AZ22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AZ22" cm="1">
-        <f t="array" ref="AZ22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="BA22" cm="1">
-        <f t="array" ref="BA22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BA22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BB22" cm="1">
+        <f t="array" ref="BB22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BB22" cm="1">
-        <f t="array" ref="BB22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BC22" cm="1">
+        <f t="array" ref="BC22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BC22" cm="1">
-        <f t="array" ref="BC22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="BD22" cm="1">
-        <f t="array" ref="BD22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="BD22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="BE22" cm="1">
-        <f t="array" ref="BE22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BE22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BF22" cm="1">
+        <f t="array" ref="BF22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BF22" cm="1">
-        <f t="array" ref="BF22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="BG22" cm="1">
-        <f t="array" ref="BG22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="BG22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="BH22" cm="1">
-        <f t="array" ref="BH22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BH22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BI22" cm="1">
+        <f t="array" ref="BI22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BI22" cm="1">
-        <f t="array" ref="BI22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BJ22" cm="1">
+        <f t="array" ref="BJ22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="BJ22" cm="1">
-        <f t="array" ref="BJ22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="BK22" cm="1">
-        <f t="array" ref="BK22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD22, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
-      <c r="BL22" cm="1">
-        <f t="array" ref="BL22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AE22, '[1]Letter Encodings'!$A:$A), '[1]Letter Encodings'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="BO22">
-        <f t="shared" si="1"/>
+        <f t="array" ref="BK22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC22, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BL22" t="e" cm="1">
+        <f t="array" ref="BL22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD22,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BM22" t="e" cm="1">
+        <f t="array" ref="BM22">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AE22,#REF!),#REF!), 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="BP22">
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BP22" t="s">
+      <c r="BQ22" t="s">
         <v>64</v>
-      </c>
-      <c r="BQ22">
-        <v>1</v>
       </c>
       <c r="BR22">
         <v>1</v>
       </c>
-      <c r="BS22" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH22:BN22)</f>
-        <v>17, 30, 38, 40, 47, 30, 52, 45, 34, 39, 50, 52, 28, 40, 38, 41, 40, 39, 30, 39, 45, 44, 52, 26, 44, 52, 45, 33, 30, 43, 30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="BS22">
+        <v>1</v>
+      </c>
+      <c r="BT22" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -5764,127 +5245,127 @@
       <c r="Z23" t="s">
         <v>58</v>
       </c>
-      <c r="AG23">
-        <f t="shared" si="0"/>
+      <c r="AH23">
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="AH23" cm="1">
-        <f t="array" ref="AH23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI23" cm="1">
+        <f t="array" ref="AI23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AI23" cm="1">
-        <f t="array" ref="AI23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ23" cm="1">
+        <f t="array" ref="AJ23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AJ23" cm="1">
-        <f t="array" ref="AJ23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK23" cm="1">
+        <f t="array" ref="AK23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>50</v>
       </c>
-      <c r="AK23" cm="1">
-        <f t="array" ref="AK23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AL23" cm="1">
-        <f t="array" ref="AL23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AL23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AM23" cm="1">
+        <f t="array" ref="AM23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AM23" cm="1">
-        <f t="array" ref="AM23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AN23" cm="1">
-        <f t="array" ref="AN23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AN23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AO23" cm="1">
-        <f t="array" ref="AO23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AO23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AP23" cm="1">
+        <f t="array" ref="AP23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AP23" cm="1">
-        <f t="array" ref="AP23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ23" cm="1">
+        <f t="array" ref="AQ23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AQ23" cm="1">
-        <f t="array" ref="AQ23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AR23" cm="1">
-        <f t="array" ref="AR23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="AR23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
       </c>
       <c r="AS23" cm="1">
-        <f t="array" ref="AS23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
+        <f t="array" ref="AS23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="AT23" cm="1">
-        <f t="array" ref="AT23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AT23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AU23" cm="1">
+        <f t="array" ref="AU23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AU23" cm="1">
-        <f t="array" ref="AU23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AV23" cm="1">
-        <f t="array" ref="AV23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AV23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AW23" cm="1">
+        <f t="array" ref="AW23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AW23" cm="1">
-        <f t="array" ref="AW23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AX23" cm="1">
+        <f t="array" ref="AX23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>50</v>
       </c>
-      <c r="AX23" cm="1">
-        <f t="array" ref="AX23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AY23" cm="1">
-        <f t="array" ref="AY23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AY23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AZ23" cm="1">
+        <f t="array" ref="AZ23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AZ23" cm="1">
-        <f t="array" ref="AZ23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="BA23" cm="1">
-        <f t="array" ref="BA23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BA23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BB23" cm="1">
+        <f t="array" ref="BB23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BB23" cm="1">
-        <f t="array" ref="BB23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="BC23" cm="1">
-        <f t="array" ref="BC23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BC23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BD23" cm="1">
+        <f t="array" ref="BD23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BD23" cm="1">
-        <f t="array" ref="BD23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="BE23" cm="1">
-        <f t="array" ref="BE23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
+        <f t="array" ref="BE23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="BF23" cm="1">
-        <f t="array" ref="BF23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BF23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BG23" cm="1">
+        <f t="array" ref="BG23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BG23" cm="1">
-        <f t="array" ref="BG23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BH23" cm="1">
+        <f t="array" ref="BH23">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z23, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="BO23">
-        <f t="shared" si="1"/>
+      <c r="BP23">
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="BR23">
+      <c r="BS23">
         <v>2</v>
       </c>
-      <c r="BS23" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH23:BN23)</f>
+      <c r="BT23" t="str">
+        <f t="shared" si="0"/>
         <v>38, 26, 50, 52, 27, 30, 52, 39, 40, 34, 44, 30, 53, 52, 27, 50, 52, 38, 34, 39, 52, 26, 43, 30, 26, 54</v>
       </c>
     </row>
-    <row r="24" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -5925,186 +5406,193 @@
         <v>41</v>
       </c>
       <c r="N24" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="O24" t="s">
+        <v>56</v>
+      </c>
+      <c r="P24" t="s">
         <v>38</v>
       </c>
-      <c r="P24" t="s">
-        <v>43</v>
-      </c>
       <c r="Q24" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="R24" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="S24" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="T24" t="s">
+        <v>56</v>
+      </c>
+      <c r="U24" t="s">
         <v>32</v>
       </c>
-      <c r="U24" t="s">
-        <v>44</v>
-      </c>
       <c r="V24" t="s">
+        <v>44</v>
+      </c>
+      <c r="W24" t="s">
         <v>42</v>
       </c>
-      <c r="W24" t="s">
+      <c r="X24" t="s">
         <v>45</v>
       </c>
-      <c r="X24" t="s">
-        <v>44</v>
-      </c>
       <c r="Y24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z24" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AA24" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="AB24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC24" t="s">
         <v>49</v>
       </c>
-      <c r="AC24" t="s">
+      <c r="AD24" t="s">
         <v>60</v>
       </c>
-      <c r="AG24">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="AH24" cm="1">
-        <f t="array" ref="AH24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AH24">
+        <f>COUNTA(A24:AG24)</f>
+        <v>30</v>
+      </c>
+      <c r="AI24" cm="1">
+        <f t="array" ref="AI24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>55</v>
       </c>
-      <c r="AI24" cm="1">
-        <f t="array" ref="AI24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ24" cm="1">
+        <f t="array" ref="AJ24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AJ24" cm="1">
-        <f t="array" ref="AJ24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK24" cm="1">
+        <f t="array" ref="AK24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AK24" cm="1">
-        <f t="array" ref="AK24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL24" cm="1">
+        <f t="array" ref="AL24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="AL24" cm="1">
-        <f t="array" ref="AL24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AM24" cm="1">
-        <f t="array" ref="AM24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AN24" cm="1">
+        <f t="array" ref="AN24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AN24" cm="1">
-        <f t="array" ref="AN24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO24" cm="1">
+        <f t="array" ref="AO24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>31</v>
       </c>
-      <c r="AO24" cm="1">
-        <f t="array" ref="AO24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AP24" cm="1">
-        <f t="array" ref="AP24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AP24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AQ24" cm="1">
+        <f t="array" ref="AQ24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AQ24" cm="1">
-        <f t="array" ref="AQ24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AR24" cm="1">
-        <f t="array" ref="AR24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AR24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AS24" cm="1">
+        <f t="array" ref="AS24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="AS24" cm="1">
-        <f t="array" ref="AS24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AT24" cm="1">
-        <f t="array" ref="AT24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AT24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AU24" cm="1">
+        <f t="array" ref="AU24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AU24" cm="1">
-        <f t="array" ref="AU24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AV24" cm="1">
-        <f t="array" ref="AV24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="AV24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="AW24" cm="1">
-        <f t="array" ref="AW24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AW24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AX24" cm="1">
+        <f t="array" ref="AX24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AY24" cm="1">
+        <f t="array" ref="AY24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AX24" cm="1">
-        <f t="array" ref="AX24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
-      <c r="AY24" cm="1">
-        <f t="array" ref="AY24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AZ24" cm="1">
+        <f t="array" ref="AZ24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BA24" cm="1">
+        <f t="array" ref="BA24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AZ24" cm="1">
-        <f t="array" ref="AZ24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
-      <c r="BA24" cm="1">
-        <f t="array" ref="BA24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BB24" cm="1">
+        <f t="array" ref="BB24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BC24" cm="1">
+        <f t="array" ref="BC24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="BB24" cm="1">
-        <f t="array" ref="BB24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BD24" cm="1">
+        <f t="array" ref="BD24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BC24" cm="1">
-        <f t="array" ref="BC24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BE24" cm="1">
+        <f t="array" ref="BE24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="BD24" cm="1">
-        <f t="array" ref="BD24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BF24" cm="1">
+        <f t="array" ref="BF24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="BE24" cm="1">
-        <f t="array" ref="BE24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BG24" cm="1">
+        <f t="array" ref="BG24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BF24" cm="1">
-        <f t="array" ref="BF24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BH24" cm="1">
+        <f t="array" ref="BH24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BG24" cm="1">
-        <f t="array" ref="BG24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="BH24" cm="1">
-        <f t="array" ref="BH24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BI24" cm="1">
+        <f t="array" ref="BI24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BJ24" cm="1">
+        <f t="array" ref="BJ24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BI24" cm="1">
-        <f t="array" ref="BI24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BK24" cm="1">
+        <f t="array" ref="BK24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BJ24" cm="1">
-        <f t="array" ref="BJ24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>56</v>
-      </c>
-      <c r="BO24">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="BR24">
+      <c r="BL24" cm="1">
+        <f t="array" ref="BL24">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AD24, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>56</v>
+      </c>
+      <c r="BP24">
+        <f>COUNTA(AI24:BN24)</f>
+        <v>30</v>
+      </c>
+      <c r="BS24">
         <v>3</v>
       </c>
-      <c r="BS24" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH24:BN24)</f>
-        <v>55, 39, 40, 54, 52, 40, 31, 52, 41, 34, 49, 30, 37, 52, 34, 39, 52, 26, 52, 28, 40, 38, 41, 40, 39, 30, 39, 45, 56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="BT24" t="str">
+        <f>_xlfn.TEXTJOIN(", ",TRUE,AI24:BO24)</f>
+        <v>55, 39, 40, 54, 52, 40, 31, 52, 41, 34, 49, 30, 37, 44, 52, 34, 39, 52, 26, 52, 28, 40, 38, 41, 40, 39, 30, 39, 45, 56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -6192,142 +5680,142 @@
       <c r="AC25" t="s">
         <v>37</v>
       </c>
-      <c r="AG25">
-        <f t="shared" si="0"/>
+      <c r="AH25">
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="AH25" cm="1">
-        <f t="array" ref="AH25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AI25" cm="1">
-        <f t="array" ref="AI25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AI25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AJ25" cm="1">
+        <f t="array" ref="AJ25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="AJ25" cm="1">
-        <f t="array" ref="AJ25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK25" cm="1">
+        <f t="array" ref="AK25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AK25" cm="1">
-        <f t="array" ref="AK25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL25" cm="1">
+        <f t="array" ref="AL25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="AL25" cm="1">
-        <f t="array" ref="AL25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM25" cm="1">
+        <f t="array" ref="AM25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AM25" cm="1">
-        <f t="array" ref="AM25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AN25" cm="1">
-        <f t="array" ref="AN25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AN25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AO25" cm="1">
+        <f t="array" ref="AO25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>60</v>
       </c>
-      <c r="AO25" cm="1">
-        <f t="array" ref="AO25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AP25" cm="1">
-        <f t="array" ref="AP25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AP25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AQ25" cm="1">
+        <f t="array" ref="AQ25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AQ25" cm="1">
-        <f t="array" ref="AQ25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AR25" cm="1">
-        <f t="array" ref="AR25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AR25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AS25" cm="1">
+        <f t="array" ref="AS25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AS25" cm="1">
-        <f t="array" ref="AS25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AT25" cm="1">
+        <f t="array" ref="AT25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AT25" cm="1">
-        <f t="array" ref="AT25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="AU25" cm="1">
-        <f t="array" ref="AU25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AU25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="AV25" cm="1">
-        <f t="array" ref="AV25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AV25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AW25" cm="1">
+        <f t="array" ref="AW25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AW25" cm="1">
-        <f t="array" ref="AW25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AX25" cm="1">
+        <f t="array" ref="AX25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AX25" cm="1">
-        <f t="array" ref="AX25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AY25" cm="1">
+        <f t="array" ref="AY25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AY25" cm="1">
-        <f t="array" ref="AY25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AZ25" cm="1">
+        <f t="array" ref="AZ25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AZ25" cm="1">
-        <f t="array" ref="AZ25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BA25" cm="1">
+        <f t="array" ref="BA25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="BA25" cm="1">
-        <f t="array" ref="BA25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BB25" cm="1">
+        <f t="array" ref="BB25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BB25" cm="1">
-        <f t="array" ref="BB25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="BC25" cm="1">
-        <f t="array" ref="BC25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BC25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BD25" cm="1">
+        <f t="array" ref="BD25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BD25" cm="1">
-        <f t="array" ref="BD25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BE25" cm="1">
+        <f t="array" ref="BE25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(W25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BE25" cm="1">
-        <f t="array" ref="BE25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="BF25" cm="1">
-        <f t="array" ref="BF25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="BF25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(X25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="BG25" cm="1">
-        <f t="array" ref="BG25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BG25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Y25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BH25" cm="1">
+        <f t="array" ref="BH25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Z25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>48</v>
       </c>
-      <c r="BH25" cm="1">
-        <f t="array" ref="BH25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="BI25" cm="1">
-        <f t="array" ref="BI25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BI25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AA25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BJ25" cm="1">
+        <f t="array" ref="BJ25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AB25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BJ25" cm="1">
-        <f t="array" ref="BJ25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BK25" cm="1">
+        <f t="array" ref="BK25">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(AC25, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="BO25">
-        <f t="shared" si="1"/>
+      <c r="BP25">
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="BQ25">
+      <c r="BR25">
         <v>2</v>
       </c>
-      <c r="BR25">
+      <c r="BS25">
         <v>4</v>
       </c>
-      <c r="BS25" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH25:BN25)</f>
+      <c r="BT25" t="str">
+        <f t="shared" si="0"/>
         <v>30, 54, 32, 54, 53, 52, 60, 52, 38, 30, 26, 39, 44, 52, 28, 40, 38, 41, 40, 39, 30, 39, 45, 44, 52, 48, 34, 45, 33</v>
       </c>
     </row>
-    <row r="26" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -6394,111 +5882,111 @@
       <c r="V26" t="s">
         <v>34</v>
       </c>
-      <c r="AG26">
-        <f t="shared" si="0"/>
+      <c r="AH26">
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="AH26" cm="1">
-        <f t="array" ref="AH26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI26" cm="1">
+        <f t="array" ref="AI26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AI26" cm="1">
-        <f t="array" ref="AI26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AJ26" cm="1">
-        <f t="array" ref="AJ26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="AJ26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AK26" cm="1">
-        <f t="array" ref="AK26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AK26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>44</v>
       </c>
       <c r="AL26" cm="1">
-        <f t="array" ref="AL26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AL26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="AM26" cm="1">
-        <f t="array" ref="AM26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AN26" cm="1">
+        <f t="array" ref="AN26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AN26" cm="1">
-        <f t="array" ref="AN26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO26" cm="1">
+        <f t="array" ref="AO26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AO26" cm="1">
-        <f t="array" ref="AO26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP26" cm="1">
+        <f t="array" ref="AP26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AP26" cm="1">
-        <f t="array" ref="AP26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ26" cm="1">
+        <f t="array" ref="AQ26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AQ26" cm="1">
-        <f t="array" ref="AQ26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AR26" cm="1">
-        <f t="array" ref="AR26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AR26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AS26" cm="1">
+        <f t="array" ref="AS26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>60</v>
       </c>
-      <c r="AS26" cm="1">
-        <f t="array" ref="AS26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AT26" cm="1">
-        <f t="array" ref="AT26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AT26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AU26" cm="1">
+        <f t="array" ref="AU26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AU26" cm="1">
-        <f t="array" ref="AU26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AV26" cm="1">
-        <f t="array" ref="AV26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AV26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AW26" cm="1">
+        <f t="array" ref="AW26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="AW26" cm="1">
-        <f t="array" ref="AW26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AX26" cm="1">
-        <f t="array" ref="AX26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AY26" cm="1">
+        <f t="array" ref="AY26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AY26" cm="1">
-        <f t="array" ref="AY26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="AZ26" cm="1">
-        <f t="array" ref="AZ26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AZ26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="BA26" cm="1">
-        <f t="array" ref="BA26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="BA26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BB26" cm="1">
+        <f t="array" ref="BB26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="BB26" cm="1">
-        <f t="array" ref="BB26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="BC26" cm="1">
-        <f t="array" ref="BC26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="BO26">
-        <f t="shared" si="1"/>
+        <f t="array" ref="BC26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="BD26" cm="1">
+        <f t="array" ref="BD26">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V26, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BP26">
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="BR26">
+      <c r="BS26">
         <v>5</v>
       </c>
-      <c r="BS26" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH26:BN26)</f>
+      <c r="BT26" t="str">
+        <f t="shared" si="0"/>
         <v>37, 30, 44, 44, 52, 45, 33, 26, 39, 52, 60, 52, 41, 34, 49, 30, 37, 44, 52, 26, 43, 30</v>
       </c>
     </row>
-    <row r="27" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -6523,65 +6011,65 @@
       <c r="H27" t="s">
         <v>58</v>
       </c>
-      <c r="AG27">
-        <f t="shared" si="0"/>
+      <c r="AH27">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="AH27" cm="1">
-        <f t="array" ref="AH27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AI27" cm="1">
-        <f t="array" ref="AI27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AI27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AJ27" cm="1">
+        <f t="array" ref="AJ27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AJ27" cm="1">
-        <f t="array" ref="AJ27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK27" cm="1">
+        <f t="array" ref="AK27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>47</v>
       </c>
-      <c r="AK27" cm="1">
-        <f t="array" ref="AK27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL27" cm="1">
+        <f t="array" ref="AL27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AL27" cm="1">
-        <f t="array" ref="AL27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM27" cm="1">
+        <f t="array" ref="AM27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AM27" cm="1">
-        <f t="array" ref="AM27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AN27" cm="1">
-        <f t="array" ref="AN27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AN27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AO27" cm="1">
+        <f t="array" ref="AO27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AO27" cm="1">
-        <f t="array" ref="AO27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP27" cm="1">
+        <f t="array" ref="AP27">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H27, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="BO27">
-        <f t="shared" si="1"/>
+      <c r="BP27">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="BR27">
+      <c r="BS27">
         <v>6</v>
       </c>
-      <c r="BS27" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH27:BN27)</f>
+      <c r="BT27" t="str">
+        <f t="shared" si="0"/>
         <v>34, 39, 47, 26, 37, 34, 29, 54</v>
       </c>
     </row>
-    <row r="28" spans="1:71" x14ac:dyDescent="0.3">
-      <c r="AG28">
-        <f t="shared" si="0"/>
+    <row r="28" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="AH28">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BS28" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH28:BN28)</f>
+      <c r="BT28" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -6615,73 +6103,73 @@
       <c r="K29" t="s">
         <v>56</v>
       </c>
-      <c r="AG29">
-        <f t="shared" si="0"/>
+      <c r="AH29">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="AH29" cm="1">
-        <f t="array" ref="AH29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI29" cm="1">
+        <f t="array" ref="AI29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>15</v>
       </c>
-      <c r="AI29" cm="1">
-        <f t="array" ref="AI29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AJ29" cm="1">
-        <f t="array" ref="AJ29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AJ29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AK29" cm="1">
+        <f t="array" ref="AK29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AK29" cm="1">
-        <f t="array" ref="AK29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AL29" cm="1">
+        <f t="array" ref="AL29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>36</v>
       </c>
-      <c r="AL29" cm="1">
-        <f t="array" ref="AL29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AM29" cm="1">
-        <f t="array" ref="AM29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AN29" cm="1">
+        <f t="array" ref="AN29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>46</v>
       </c>
-      <c r="AN29" cm="1">
-        <f t="array" ref="AN29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO29" cm="1">
+        <f t="array" ref="AO29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AO29" cm="1">
-        <f t="array" ref="AO29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AP29" cm="1">
-        <f t="array" ref="AP29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AP29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AQ29" cm="1">
+        <f t="array" ref="AQ29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AQ29" cm="1">
-        <f t="array" ref="AQ29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR29" cm="1">
+        <f t="array" ref="AR29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AR29" cm="1">
-        <f t="array" ref="AR29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
-      <c r="BO29">
-        <f t="shared" si="1"/>
+      <c r="AS29" cm="1">
+        <f t="array" ref="AS29">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K29, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="BP29">
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="BP29" t="s">
+      <c r="BQ29" t="s">
         <v>65</v>
-      </c>
-      <c r="BQ29">
-        <v>1</v>
       </c>
       <c r="BR29">
         <v>1</v>
       </c>
-      <c r="BS29" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH29:BN29)</f>
+      <c r="BS29">
+        <v>1</v>
+      </c>
+      <c r="BT29" t="str">
+        <f t="shared" si="0"/>
         <v>15, 34, 28, 36, 52, 46, 41, 52, 45, 40, 52</v>
       </c>
     </row>
-    <row r="30" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1</v>
       </c>
@@ -6730,87 +6218,87 @@
       <c r="P30">
         <v>4</v>
       </c>
-      <c r="AG30">
-        <f t="shared" si="0"/>
+      <c r="AH30">
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="AH30" cm="1">
-        <f t="array" ref="AH30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI30" cm="1">
+        <f t="array" ref="AI30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>57</v>
       </c>
-      <c r="AI30" cm="1">
-        <f t="array" ref="AI30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AJ30" cm="1">
-        <f t="array" ref="AJ30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AJ30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AK30" cm="1">
+        <f t="array" ref="AK30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AK30" cm="1">
-        <f t="array" ref="AK30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AL30" cm="1">
-        <f t="array" ref="AL30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AL30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AM30" cm="1">
-        <f t="array" ref="AM30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AN30" cm="1">
+        <f t="array" ref="AN30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>58</v>
       </c>
-      <c r="AN30" cm="1">
-        <f t="array" ref="AN30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AO30" cm="1">
-        <f t="array" ref="AO30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AO30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AP30" cm="1">
+        <f t="array" ref="AP30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AP30" cm="1">
-        <f t="array" ref="AP30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AQ30" cm="1">
-        <f t="array" ref="AQ30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AQ30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AR30" cm="1">
-        <f t="array" ref="AR30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AR30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AS30" cm="1">
+        <f t="array" ref="AS30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>59</v>
       </c>
-      <c r="AS30" cm="1">
-        <f t="array" ref="AS30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AT30" cm="1">
-        <f t="array" ref="AT30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AT30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AU30" cm="1">
+        <f t="array" ref="AU30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AU30" cm="1">
-        <f t="array" ref="AU30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AV30" cm="1">
-        <f t="array" ref="AV30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AV30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AW30" cm="1">
-        <f t="array" ref="AW30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AW30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AX30" cm="1">
+        <f t="array" ref="AX30">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P30, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>60</v>
       </c>
-      <c r="BO30">
-        <f t="shared" si="1"/>
+      <c r="BP30">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="BR30">
+      <c r="BS30">
         <v>2</v>
       </c>
-      <c r="BS30" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH30:BN30)</f>
+      <c r="BT30" t="str">
+        <f t="shared" si="0"/>
         <v>57, 52, 40, 43, 52, 58, 52, 40, 43, 52, 59, 52, 40, 43, 52, 60</v>
       </c>
     </row>
-    <row r="31" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>51</v>
       </c>
@@ -6862,91 +6350,91 @@
       <c r="Q31" t="s">
         <v>58</v>
       </c>
-      <c r="AG31">
-        <f t="shared" si="0"/>
+      <c r="AH31">
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="AH31" cm="1">
-        <f t="array" ref="AH31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI31" cm="1">
+        <f t="array" ref="AI31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>47</v>
       </c>
-      <c r="AI31" cm="1">
-        <f t="array" ref="AI31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ31" cm="1">
+        <f t="array" ref="AJ31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AJ31" cm="1">
-        <f t="array" ref="AJ31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AK31" cm="1">
+        <f t="array" ref="AK31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>37</v>
       </c>
-      <c r="AK31" cm="1">
-        <f t="array" ref="AK31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AL31" cm="1">
-        <f t="array" ref="AL31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AL31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AM31" cm="1">
+        <f t="array" ref="AM31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AM31" cm="1">
-        <f t="array" ref="AM31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AN31" cm="1">
-        <f t="array" ref="AN31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AN31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AO31" cm="1">
+        <f t="array" ref="AO31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AO31" cm="1">
-        <f t="array" ref="AO31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP31" cm="1">
+        <f t="array" ref="AP31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AP31" cm="1">
-        <f t="array" ref="AP31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AQ31" cm="1">
+        <f t="array" ref="AQ31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AQ31" cm="1">
-        <f t="array" ref="AQ31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR31" cm="1">
+        <f t="array" ref="AR31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AR31" cm="1">
-        <f t="array" ref="AR31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AS31" cm="1">
+        <f t="array" ref="AS31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AS31" cm="1">
-        <f t="array" ref="AS31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AT31" cm="1">
+        <f t="array" ref="AT31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AT31" cm="1">
-        <f t="array" ref="AT31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AU31" cm="1">
-        <f t="array" ref="AU31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AU31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AV31" cm="1">
+        <f t="array" ref="AV31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AV31" cm="1">
-        <f t="array" ref="AV31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AW31" cm="1">
+        <f t="array" ref="AW31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AW31" cm="1">
-        <f t="array" ref="AW31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="AX31" cm="1">
-        <f t="array" ref="AX31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="AY31" cm="1">
+        <f t="array" ref="AY31">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q31, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="BO31">
-        <f t="shared" si="1"/>
+      <c r="BP31">
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="BR31">
+      <c r="BS31">
         <v>3</v>
       </c>
-      <c r="BS31" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH31:BN31)</f>
+      <c r="BT31" t="str">
+        <f t="shared" si="0"/>
         <v>47, 26, 37, 34, 29, 52, 28, 40, 38, 41, 40, 39, 30, 39, 45, 44, 54</v>
       </c>
     </row>
-    <row r="32" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -7013,114 +6501,114 @@
       <c r="V32" t="s">
         <v>34</v>
       </c>
-      <c r="AG32">
-        <f t="shared" si="0"/>
+      <c r="AH32">
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="AH32" cm="1">
-        <f t="array" ref="AH32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI32" cm="1">
+        <f t="array" ref="AI32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>20</v>
       </c>
-      <c r="AI32" cm="1">
-        <f t="array" ref="AI32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
-      </c>
       <c r="AJ32" cm="1">
-        <f t="array" ref="AJ32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="AJ32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
       </c>
       <c r="AK32" cm="1">
-        <f t="array" ref="AK32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AK32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AL32" cm="1">
+        <f t="array" ref="AL32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AL32" cm="1">
-        <f t="array" ref="AL32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM32" cm="1">
+        <f t="array" ref="AM32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>32</v>
       </c>
-      <c r="AM32" cm="1">
-        <f t="array" ref="AM32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AN32" cm="1">
-        <f t="array" ref="AN32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AN32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AO32" cm="1">
+        <f t="array" ref="AO32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AO32" cm="1">
-        <f t="array" ref="AO32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AP32" cm="1">
-        <f t="array" ref="AP32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AP32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AQ32" cm="1">
+        <f t="array" ref="AQ32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="AQ32" cm="1">
-        <f t="array" ref="AQ32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AR32" cm="1">
+        <f t="array" ref="AR32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AR32" cm="1">
-        <f t="array" ref="AR32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AS32" cm="1">
-        <f t="array" ref="AS32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AT32" cm="1">
+        <f t="array" ref="AT32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>38</v>
       </c>
-      <c r="AT32" cm="1">
-        <f t="array" ref="AT32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AU32" cm="1">
+        <f t="array" ref="AU32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AU32" cm="1">
-        <f t="array" ref="AU32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AV32" cm="1">
+        <f t="array" ref="AV32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="AV32" cm="1">
-        <f t="array" ref="AV32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AW32" cm="1">
+        <f t="array" ref="AW32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AW32" cm="1">
-        <f t="array" ref="AW32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AX32" cm="1">
-        <f t="array" ref="AX32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AY32" cm="1">
+        <f t="array" ref="AY32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AY32" cm="1">
-        <f t="array" ref="AY32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AZ32" cm="1">
-        <f t="array" ref="AZ32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AZ32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BA32" cm="1">
+        <f t="array" ref="BA32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>39</v>
       </c>
-      <c r="BA32" cm="1">
-        <f t="array" ref="BA32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="BB32" cm="1">
+        <f t="array" ref="BB32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(T32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="BB32" cm="1">
-        <f t="array" ref="BB32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="BC32" cm="1">
-        <f t="array" ref="BC32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="BO32">
-        <f t="shared" si="1"/>
+        <f t="array" ref="BC32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(U32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="BD32" cm="1">
+        <f t="array" ref="BD32">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(V32, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="BP32">
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="BQ32">
+      <c r="BR32">
         <v>2</v>
       </c>
-      <c r="BR32">
+      <c r="BS32">
         <v>4</v>
       </c>
-      <c r="BS32" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH32:BN32)</f>
+      <c r="BT32" t="str">
+        <f t="shared" si="0"/>
         <v>20, 44, 34, 39, 32, 52, 38, 34, 39, 53, 52, 38, 26, 49, 53, 52, 28, 30, 39, 45, 43, 30</v>
       </c>
     </row>
-    <row r="33" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -7178,99 +6666,99 @@
       <c r="S33" t="s">
         <v>47</v>
       </c>
-      <c r="AG33">
-        <f t="shared" si="0"/>
+      <c r="AH33">
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="AH33" cm="1">
-        <f t="array" ref="AH33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AI33" cm="1">
+        <f t="array" ref="AI33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AI33" cm="1">
-        <f t="array" ref="AI33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AJ33" cm="1">
+        <f t="array" ref="AJ33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>31</v>
       </c>
-      <c r="AJ33" cm="1">
-        <f t="array" ref="AJ33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AK33" cm="1">
-        <f t="array" ref="AK33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AK33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AL33" cm="1">
+        <f t="array" ref="AL33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="AL33" cm="1">
-        <f t="array" ref="AL33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AM33" cm="1">
+        <f t="array" ref="AM33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AM33" cm="1">
-        <f t="array" ref="AM33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AN33" cm="1">
-        <f t="array" ref="AN33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AN33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AO33" cm="1">
+        <f t="array" ref="AO33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>50</v>
       </c>
-      <c r="AO33" cm="1">
-        <f t="array" ref="AO33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AP33" cm="1">
+        <f t="array" ref="AP33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>53</v>
       </c>
-      <c r="AP33" cm="1">
-        <f t="array" ref="AP33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AQ33" cm="1">
-        <f t="array" ref="AQ33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AQ33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AR33" cm="1">
+        <f t="array" ref="AR33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>29</v>
       </c>
-      <c r="AR33" cm="1">
-        <f t="array" ref="AR33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AS33" cm="1">
-        <f t="array" ref="AS33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="AT33" cm="1">
+        <f t="array" ref="AT33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AT33" cm="1">
-        <f t="array" ref="AT33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AU33" cm="1">
+        <f t="array" ref="AU33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>48</v>
       </c>
-      <c r="AU33" cm="1">
-        <f t="array" ref="AU33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
-      </c>
       <c r="AV33" cm="1">
-        <f t="array" ref="AV33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AV33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AW33" cm="1">
+        <f t="array" ref="AW33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AW33" cm="1">
-        <f t="array" ref="AW33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AX33" cm="1">
+        <f t="array" ref="AX33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>33</v>
       </c>
-      <c r="AX33" cm="1">
-        <f t="array" ref="AX33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AY33" cm="1">
-        <f t="array" ref="AY33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
+        <f t="array" ref="AY33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AZ33" cm="1">
-        <f t="array" ref="AZ33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
-      <c r="BO33">
-        <f t="shared" si="1"/>
+        <f t="array" ref="AZ33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(R33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="BA33" cm="1">
+        <f t="array" ref="BA33">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(S33, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="BP33">
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="BR33">
+      <c r="BS33">
         <v>5</v>
       </c>
-      <c r="BS33" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH33:BN33)</f>
+      <c r="BT33" t="str">
+        <f t="shared" si="0"/>
         <v>40, 31, 52, 49, 53, 52, 50, 53, 52, 29, 43, 26, 48, 52, 45, 33, 30, 34, 43</v>
       </c>
     </row>
-    <row r="34" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -7322,87 +6810,87 @@
       <c r="Q34" t="s">
         <v>58</v>
       </c>
-      <c r="AG34">
-        <f t="shared" si="0"/>
+      <c r="AH34">
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="AH34" cm="1">
-        <f t="array" ref="AH34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>43</v>
-      </c>
       <c r="AI34" cm="1">
-        <f t="array" ref="AI34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
+        <f t="array" ref="AI34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(A34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>43</v>
       </c>
       <c r="AJ34" cm="1">
-        <f t="array" ref="AJ34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="AJ34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(B34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AK34" cm="1">
-        <f t="array" ref="AK34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AK34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(C34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="AL34" cm="1">
+        <f t="array" ref="AL34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(D34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>41</v>
       </c>
-      <c r="AL34" cm="1">
-        <f t="array" ref="AL34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AM34" cm="1">
-        <f t="array" ref="AM34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AM34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(E34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="AN34" cm="1">
+        <f t="array" ref="AN34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(F34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>28</v>
       </c>
-      <c r="AN34" cm="1">
-        <f t="array" ref="AN34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AO34" cm="1">
+        <f t="array" ref="AO34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(G34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AO34" cm="1">
-        <f t="array" ref="AO34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>34</v>
-      </c>
       <c r="AP34" cm="1">
-        <f t="array" ref="AP34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AP34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(H34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="AQ34" cm="1">
+        <f t="array" ref="AQ34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(I34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>47</v>
       </c>
-      <c r="AQ34" cm="1">
-        <f t="array" ref="AQ34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AR34" cm="1">
-        <f t="array" ref="AR34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>52</v>
+        <f t="array" ref="AR34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(J34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AS34" cm="1">
-        <f t="array" ref="AS34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AS34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(K34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="AT34" cm="1">
+        <f t="array" ref="AT34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(L34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>27</v>
       </c>
-      <c r="AT34" cm="1">
-        <f t="array" ref="AT34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AU34" cm="1">
+        <f t="array" ref="AU34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(M34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="AU34" cm="1">
-        <f t="array" ref="AU34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+      <c r="AV34" cm="1">
+        <f t="array" ref="AV34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(N34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>49</v>
       </c>
-      <c r="AV34" cm="1">
-        <f t="array" ref="AV34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>30</v>
-      </c>
       <c r="AW34" cm="1">
-        <f t="array" ref="AW34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
-        <v>44</v>
+        <f t="array" ref="AW34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(O34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>30</v>
       </c>
       <c r="AX34" cm="1">
-        <f t="array" ref="AX34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <f t="array" ref="AX34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(P34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="AY34" cm="1">
+        <f t="array" ref="AY34">VLOOKUP(TRUE, CHOOSE({1,2}, EXACT(Q34, 'Letter Encoding'!$A:$A), 'Letter Encoding'!$C:$C), 2, FALSE)</f>
         <v>54</v>
       </c>
-      <c r="BO34">
-        <f t="shared" si="1"/>
+      <c r="BP34">
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="BR34">
+      <c r="BS34">
         <v>6</v>
       </c>
-      <c r="BS34" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,AH34:BN34)</f>
+      <c r="BT34" t="str">
+        <f t="shared" si="0"/>
         <v>43, 30, 44, 41, 30, 28, 45, 34, 47, 30, 52, 27, 40, 49, 30, 44, 54</v>
       </c>
     </row>
